--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ANCONA</t>
+          <t>FIP PROMISES LISBOA II</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -595,16 +595,20 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-promises-lisboa-ii/</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>46334</v>
+      </c>
       <c r="L2" s="3" t="n">
         <v>46316</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="4" t="n"/>
@@ -614,7 +618,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46310.70134993114</v>
+        <v>46310.99538540662</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -625,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LISBOA II</t>
+          <t>FIP PROMISES ANCONA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -635,12 +639,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -657,16 +661,20 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lisboa-ii/</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>46334</v>
+      </c>
       <c r="L3" s="3" t="n">
         <v>46316</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="4" t="n"/>
@@ -676,7 +684,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46310.70135835974</v>
+        <v>46310.99539377838</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -722,13 +730,17 @@
           <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
+      <c r="J4" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="L4" s="3" t="n">
         <v>46323</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="4" t="n"/>
@@ -738,7 +750,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46310.70136659937</v>
+        <v>46310.99540226066</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -784,13 +796,17 @@
           <t>https://www.padelfip.com/events/fip-promises-valencia-2026-2/</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="J5" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="L5" s="3" t="n">
         <v>46323</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="4" t="n"/>
@@ -800,7 +816,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46310.70137499613</v>
+        <v>46310.99541067053</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -842,13 +858,17 @@
           <t>https://www.padelfip.com/events/fip-promises-ketameya-heights-2026/</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="J6" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="L6" s="3" t="n">
         <v>46323</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="4" t="n"/>
@@ -858,7 +878,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46310.70138323087</v>
+        <v>46310.99541885596</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -904,13 +924,17 @@
           <t>https://www.padelfip.com/events/fip-promises-doha-iii/</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
+      <c r="J7" s="3" t="n">
+        <v>46344</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L7" s="3" t="n">
         <v>46330</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="4" t="n"/>
@@ -920,7 +944,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46310.70139195153</v>
+        <v>46310.99542759103</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -931,7 +955,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES PERUGIA III</t>
+          <t>FIP PROMISES ROESELARE</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -941,12 +965,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -963,16 +987,20 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>46345</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L8" s="3" t="n">
         <v>46330</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="4" t="n"/>
@@ -982,7 +1010,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46310.70140030999</v>
+        <v>46310.99543599089</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -993,7 +1021,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ROESELARE</t>
+          <t>FIP PROMISES PERUGIA III</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1003,12 +1031,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -1025,16 +1053,20 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>46345</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L9" s="3" t="n">
         <v>46330</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="4" t="n"/>
@@ -1044,7 +1076,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46310.70140861983</v>
+        <v>46310.99544448769</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1086,13 +1118,17 @@
           <t>https://www.padelfip.com/events/fip-promises-hong-kong-v/</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
+      <c r="J10" s="3" t="n">
+        <v>46346</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>46330</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="4" t="n"/>
@@ -1102,7 +1138,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46310.70141667769</v>
+        <v>46310.99545324255</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1149,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES RENDE</t>
+          <t>FIP PROMISES LLEIDA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1123,12 +1159,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Rende</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -1138,19 +1174,27 @@
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>46352</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>46355</v>
+      </c>
       <c r="L11" s="3" t="n">
         <v>46337</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="4" t="n"/>
@@ -1160,7 +1204,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46310.70142505575</v>
+        <v>46310.99546162318</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1171,7 +1215,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LLEIDA</t>
+          <t>FIP PROMISES RENDE</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1181,12 +1225,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Rende</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -1196,23 +1240,23 @@
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>46352</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>46355</v>
+      </c>
       <c r="L12" s="3" t="n">
         <v>46337</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="4" t="n"/>
@@ -1222,7 +1266,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46310.70143331441</v>
+        <v>46310.99546992606</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1268,13 +1312,17 @@
           <t>https://www.padelfip.com/events/fip-silver-damac-dubai-ii-2026/</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
+      <c r="J13" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>46327</v>
+      </c>
       <c r="L13" s="3" t="n">
         <v>46311</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="4" t="n"/>
@@ -1284,7 +1332,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46310.70144144154</v>
+        <v>46310.99547826118</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1330,13 +1378,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-ko-panghan/</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
+      <c r="J14" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46327</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>46311</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="4" t="n"/>
@@ -1346,7 +1398,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46310.70144964266</v>
+        <v>46310.99548668493</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1392,13 +1444,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-tashkent-2026/</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="J15" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>46327</v>
+      </c>
       <c r="L15" s="3" t="n">
         <v>46311</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="4" t="n"/>
@@ -1408,7 +1464,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46310.70145829023</v>
+        <v>46310.99549519308</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1454,13 +1510,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-jc-ferrero-academy-2026/</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
+      <c r="J16" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>46327</v>
+      </c>
       <c r="L16" s="3" t="n">
         <v>46311</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="4" t="n"/>
@@ -1470,7 +1530,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46310.70146661918</v>
+        <v>46310.99550356094</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1512,13 +1572,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-cyprus-iii-2026/</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+      <c r="J17" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>46327</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>46311</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="4" t="n"/>
@@ -1528,7 +1592,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46310.70147491887</v>
+        <v>46310.99551194775</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1574,13 +1638,17 @@
           <t>https://www.padelfip.com/events/fip-gold-mediolanum-torino-2026/</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+      <c r="J18" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>46327</v>
+      </c>
       <c r="L18" s="3" t="n">
         <v>46311</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="4" t="n"/>
@@ -1590,7 +1658,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46310.70148359801</v>
+        <v>46310.99552034237</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1632,13 +1700,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
+      <c r="J19" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>46334</v>
+      </c>
       <c r="L19" s="3" t="n">
         <v>46318</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="4" t="n"/>
@@ -1648,7 +1720,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46310.70149173667</v>
+        <v>46310.99552876772</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1694,13 +1766,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
+      <c r="J20" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>46334</v>
+      </c>
       <c r="L20" s="3" t="n">
         <v>46318</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="4" t="n"/>
@@ -1710,7 +1786,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46310.70150243909</v>
+        <v>46310.99553779812</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -1756,13 +1832,17 @@
           <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
+      <c r="J21" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>46334</v>
+      </c>
       <c r="L21" s="3" t="n">
         <v>46318</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="4" t="n"/>
@@ -1772,7 +1852,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46310.70151042759</v>
+        <v>46310.99554620633</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -1783,7 +1863,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1793,18 +1873,18 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1815,16 +1895,20 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="L22" s="3" t="n">
         <v>46325</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N22" s="3" t="n"/>
       <c r="O22" s="4" t="n"/>
@@ -1834,7 +1918,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46310.70151861288</v>
+        <v>46310.99555505935</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -1845,7 +1929,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOHA II</t>
+          <t>FIP BRONZE PALA PADEL NOLA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1855,12 +1939,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Nola</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -1877,16 +1961,20 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-bronze-pala-padel-nola-2026/</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="L23" s="3" t="n">
         <v>46325</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="4" t="n"/>
@@ -1896,7 +1984,7 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46310.70152703015</v>
+        <v>46310.99556348645</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -1907,7 +1995,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE PALA PADEL NOLA</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1917,7 +2005,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nola</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1939,16 +2027,20 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-pala-padel-nola-2026/</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>46325</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="4" t="n"/>
@@ -1958,7 +2050,7 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46310.70153540588</v>
+        <v>46310.99557191032</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -1969,7 +2061,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MEDIOLANUM COMO</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1979,18 +2071,18 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -2001,16 +2093,20 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>46341</v>
+      </c>
       <c r="L25" s="3" t="n">
         <v>46325</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="4" t="n"/>
@@ -2020,7 +2116,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46310.70154353213</v>
+        <v>46310.9955806318</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2066,13 +2162,17 @@
           <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
+      <c r="J26" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>46347</v>
+      </c>
       <c r="L26" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="4" t="n"/>
@@ -2082,7 +2182,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46310.70155189894</v>
+        <v>46310.99558903659</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2128,13 +2228,17 @@
           <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
+      <c r="J27" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L27" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="4" t="n"/>
@@ -2144,7 +2248,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46310.70156023986</v>
+        <v>46310.99559743765</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2190,13 +2294,17 @@
           <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
+      <c r="J28" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L28" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="4" t="n"/>
@@ -2206,7 +2314,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46310.70156855169</v>
+        <v>46310.99560600073</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2252,13 +2360,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
+      <c r="J29" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>46347</v>
+      </c>
       <c r="L29" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="4" t="n"/>
@@ -2268,7 +2380,7 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46310.70157713004</v>
+        <v>46310.99561448007</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2314,8 +2426,12 @@
           <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
+      <c r="J30" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="3" t="n"/>
@@ -2326,7 +2442,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46310.70159790955</v>
+        <v>46310.99562288399</v>
       </c>
       <c r="R30" s="2" t="n"/>
     </row>
@@ -2368,13 +2484,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
+      <c r="J31" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="4" t="n"/>
@@ -2384,7 +2504,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46310.70160727208</v>
+        <v>46310.99563142379</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2430,13 +2550,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
+      <c r="J32" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L32" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="4" t="n"/>
@@ -2446,7 +2570,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46310.70161614906</v>
+        <v>46310.9956401821</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2492,13 +2616,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
+      <c r="J33" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L33" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="4" t="n"/>
@@ -2508,7 +2636,7 @@
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46310.7016244604</v>
+        <v>46310.99564867714</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -2554,13 +2682,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
+      <c r="J34" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>46348</v>
+      </c>
       <c r="L34" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N34" s="3" t="n"/>
       <c r="O34" s="4" t="n"/>
@@ -2570,7 +2702,7 @@
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46310.70163312437</v>
+        <v>46310.99565699469</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -2612,13 +2744,17 @@
           <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
+      <c r="J35" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>46355</v>
+      </c>
       <c r="L35" s="3" t="n">
         <v>46339</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N35" s="3" t="n"/>
       <c r="O35" s="4" t="n"/>
@@ -2628,7 +2764,7 @@
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46310.70164118568</v>
+        <v>46310.99566548628</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -2670,13 +2806,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
+      <c r="J36" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>46355</v>
+      </c>
       <c r="L36" s="3" t="n">
         <v>46339</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="4" t="n"/>
@@ -2686,7 +2826,7 @@
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46310.70164954704</v>
+        <v>46310.99567394408</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -2732,13 +2872,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
+      <c r="J37" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>46355</v>
+      </c>
       <c r="L37" s="3" t="n">
         <v>46339</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="4" t="n"/>
@@ -2748,7 +2892,7 @@
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46310.70165780611</v>
+        <v>46310.99568231885</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -2790,13 +2934,17 @@
           <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
         </is>
       </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
+      <c r="J38" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>46355</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>46339</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="4" t="n"/>
@@ -2806,7 +2954,7 @@
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46310.70166673377</v>
+        <v>46310.99569067036</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -2876,7 +3024,7 @@
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46310.70168005783</v>
+        <v>46310.99570412544</v>
       </c>
       <c r="R39" s="2" t="n"/>
     </row>
@@ -2942,7 +3090,7 @@
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46310.70168007092</v>
+        <v>46310.99570413851</v>
       </c>
       <c r="R40" s="2" t="n"/>
     </row>
@@ -3016,7 +3164,7 @@
         </is>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>46310.7016800947</v>
+        <v>46310.99570416055</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -3094,7 +3242,7 @@
         </is>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>46310.70168010749</v>
+        <v>46310.99570417334</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -3172,7 +3320,7 @@
         </is>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>46310.70168012639</v>
+        <v>46310.99570419111</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -3250,7 +3398,7 @@
         </is>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>46310.70168013899</v>
+        <v>46310.9957042032</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -3328,7 +3476,7 @@
         </is>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>46310.70168015491</v>
+        <v>46310.99570421919</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3554,7 @@
         </is>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>46310.70168016757</v>
+        <v>46310.9957042317</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -3484,7 +3632,7 @@
         </is>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>46310.7016801854</v>
+        <v>46310.99570424893</v>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
@@ -3562,7 +3710,7 @@
         </is>
       </c>
       <c r="Q48" s="5" t="n">
-        <v>46310.70168019665</v>
+        <v>46310.99570426017</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -3628,7 +3776,7 @@
         </is>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>46310.70168022714</v>
+        <v>46310.99570428999</v>
       </c>
       <c r="R49" s="2" t="n"/>
     </row>

--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$R$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$R$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,11 +445,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46310.99538540662</v>
+        <v>46311.0089223972</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46310.99539377838</v>
+        <v>46311.00893074444</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46310.99540226066</v>
+        <v>46311.00893889521</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46310.99541067053</v>
+        <v>46311.00894758235</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46310.99541885596</v>
+        <v>46311.00895580083</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46310.99542759103</v>
+        <v>46311.00896443993</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46310.99543599089</v>
+        <v>46311.00897311972</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46310.99544448769</v>
+        <v>46311.00898164184</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46310.99545324255</v>
+        <v>46311.00898979608</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46310.99546162318</v>
+        <v>46311.00899808338</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46310.99546992606</v>
+        <v>46311.00900613274</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46310.99547826118</v>
+        <v>46311.00901488433</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46310.99548668493</v>
+        <v>46311.00902307986</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46310.99549519308</v>
+        <v>46311.00903154055</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46310.99550356094</v>
+        <v>46311.00903992991</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46310.99551194775</v>
+        <v>46311.00904824762</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46310.99552034237</v>
+        <v>46311.00905667841</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46310.99552876772</v>
+        <v>46311.0090652003</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46310.99553779812</v>
+        <v>46311.00907385675</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46310.99554620633</v>
+        <v>46311.00909378632</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46310.99555505935</v>
+        <v>46311.00910207501</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46310.99556348645</v>
+        <v>46311.00911054684</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46310.99557191032</v>
+        <v>46311.00911882619</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46310.9955806318</v>
+        <v>46311.00912745361</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46310.99558903659</v>
+        <v>46311.00913566191</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46310.99559743765</v>
+        <v>46311.00914401731</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46310.99560600073</v>
+        <v>46311.00915273234</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46310.99561448007</v>
+        <v>46311.00916113639</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46310.99562288399</v>
+        <v>46311.00916981779</v>
       </c>
       <c r="R30" s="2" t="n"/>
     </row>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46310.99563142379</v>
+        <v>46311.00917870067</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46310.9956401821</v>
+        <v>46311.00918779985</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46310.99564867714</v>
+        <v>46311.00919654341</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46310.99565699469</v>
+        <v>46311.00920491044</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46310.99566548628</v>
+        <v>46311.00921347404</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46310.99567394408</v>
+        <v>46311.00922199796</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46310.99568231885</v>
+        <v>46311.00923038685</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46310.99569067036</v>
+        <v>46311.009238598</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -2965,17 +2965,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Open A-Z Padel Guimarães</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FIP (calendário TieSports)</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Mafra</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>My Padel Center</t>
+          <t>Top-padel Guimarães</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>M &amp; F</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>JUV</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3005,43 +3005,55 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>/torneios/fip-promises-jov-2026-10-12</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>46307</v>
+        <v>46316</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46313</v>
-      </c>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="4" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="4" t="n"/>
+        <v>46320</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Torneio a decorrer</t>
+          <t>Pagamentos a decorrer</t>
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46310.99570412544</v>
-      </c>
-      <c r="R39" s="2" t="n"/>
+        <v>46311.00925219018</v>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Open Oeiras Valley</t>
+          <t>5º Open Padcenter</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>FIP (calendário TieSports)</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Odivelas</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3051,12 +3063,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Oeiras Padel Academy</t>
+          <t>Padcenter Odivelas</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>M&amp;F</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3071,33 +3083,45 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenOeirasValley</t>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>46308</v>
+        <v>46317</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46313</v>
-      </c>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="4" t="n"/>
+        <v>46320</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Torneio a decorrer</t>
+          <t>Pagamentos a decorrer</t>
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46310.99570413851</v>
-      </c>
-      <c r="R40" s="2" t="n"/>
+        <v>46311.00925220264</v>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Open A-Z Padel Guimarães</t>
+          <t>1º Open de Absolutos by GRIP</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3107,7 +3131,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Pinhal Novo</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3117,7 +3141,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Top-padel Guimarães</t>
+          <t>GRIP - Grande Indoor Padel</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3137,34 +3161,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="M41" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="O41" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>46310.99570416055</v>
+        <v>46311.00925222162</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -3175,7 +3199,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>5º Open Padcenter</t>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3185,7 +3209,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Odivelas</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3195,7 +3219,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Padcenter Odivelas</t>
+          <t>Ultra Padel Club</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3215,34 +3239,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>46317</v>
+        <v>46323</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="M42" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="O42" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>46310.99570417334</v>
+        <v>46311.00925223475</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -3253,7 +3277,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos by GRIP</t>
+          <t>Open Luximos Christie's 2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3263,7 +3287,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3273,7 +3297,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>GRIP - Grande Indoor Padel</t>
+          <t>Your Top-padel Industrial</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3293,11 +3317,11 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>46327</v>
@@ -3312,7 +3336,7 @@
         <v>46317</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
@@ -3320,7 +3344,7 @@
         </is>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>46310.99570419111</v>
+        <v>46311.00925225037</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -3331,7 +3355,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
+          <t>III Open W Padel &amp; Ténis Parque</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3341,7 +3365,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3351,7 +3375,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Ultra Padel Club</t>
+          <t>W Padel Ténis &amp; Parque</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3371,17 +3395,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>46327</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="M44" s="4" t="n">
         <v>0.625</v>
@@ -3398,7 +3422,7 @@
         </is>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>46310.9957042032</v>
+        <v>46311.00925226259</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -3409,7 +3433,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Open Luximos Christie's 2026</t>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3419,7 +3443,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3429,7 +3453,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Your Top-padel Industrial</t>
+          <t>Dezporvinte</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3449,26 +3473,26 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>46315</v>
+        <v>46322</v>
       </c>
       <c r="M45" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
@@ -3476,7 +3500,7 @@
         </is>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>46310.99570421919</v>
+        <v>46311.00925228146</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -3487,7 +3511,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
+          <t>Open Caetano Auto</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3497,7 +3521,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3507,7 +3531,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>W Padel Ténis &amp; Parque</t>
+          <t>Quinta de Monserrate Gaia</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3527,23 +3551,23 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenCaetano26</t>
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="M46" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="O46" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3554,7 +3578,7 @@
         </is>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>46310.9957042317</v>
+        <v>46311.00925229386</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -3565,7 +3589,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3575,7 +3599,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3585,19 +3609,15 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Dezporvinte</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
+          <t>M &amp; F</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -3605,183 +3625,31 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>46332</v>
+        <v>46345</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N47" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46348</v>
+      </c>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="3" t="n"/>
+      <c r="O47" s="4" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>46310.99570424893</v>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Open Caetano Auto</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Vila Nova de Gaia</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Quinta de Monserrate Gaia</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenCaetano26</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N48" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="O48" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições abertas</t>
-        </is>
-      </c>
-      <c r="Q48" s="5" t="n">
-        <v>46310.99570426017</v>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>M &amp; F</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>46345</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="L49" s="3" t="n"/>
-      <c r="M49" s="4" t="n"/>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="4" t="n"/>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições fechadas</t>
-        </is>
-      </c>
-      <c r="Q49" s="5" t="n">
-        <v>46310.99570428999</v>
-      </c>
-      <c r="R49" s="2" t="n"/>
+        <v>46311.00925232578</v>
+      </c>
+      <c r="R47" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R49"/>
+  <autoFilter ref="A1:R47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -587,7 +587,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -618,7 +622,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46311.0089223972</v>
+        <v>46311.01558229799</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -653,7 +657,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -684,7 +692,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46311.00893074444</v>
+        <v>46311.01559053672</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -719,7 +727,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -750,7 +762,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46311.00893889521</v>
+        <v>46311.01559871531</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -785,7 +797,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -816,7 +832,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46311.00894758235</v>
+        <v>46311.0156069881</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -851,7 +867,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -878,7 +898,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46311.00895580083</v>
+        <v>46311.01561524518</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -913,7 +933,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -944,7 +968,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46311.00896443993</v>
+        <v>46311.01562376043</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -979,7 +1003,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -1010,7 +1038,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46311.00897311972</v>
+        <v>46311.01564137753</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1045,7 +1073,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -1076,7 +1108,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46311.00898164184</v>
+        <v>46311.01564964397</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1111,7 +1143,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1138,7 +1174,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46311.00898979608</v>
+        <v>46311.01565801506</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1173,7 +1209,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
@@ -1204,7 +1244,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46311.00899808338</v>
+        <v>46311.01566629728</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1239,7 +1279,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>JOV</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1266,7 +1310,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46311.00900613274</v>
+        <v>46311.01567451712</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1301,7 +1345,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>40 Euros per player</t>
@@ -1332,7 +1380,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46311.00901488433</v>
+        <v>46311.0156827271</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1367,7 +1415,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -1398,7 +1450,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46311.00902307986</v>
+        <v>46311.01569105346</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1433,7 +1485,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -1464,7 +1520,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46311.00903154055</v>
+        <v>46311.01569943015</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1499,7 +1555,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -1530,7 +1590,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46311.00903992991</v>
+        <v>46311.01570782824</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1561,7 +1621,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>40€ per player</t>
@@ -1592,7 +1656,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46311.00904824762</v>
+        <v>46311.01571651395</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1627,7 +1691,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>40 €</t>
@@ -1658,7 +1726,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46311.00905667841</v>
+        <v>46311.0157249788</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1757,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>40€ per player</t>
@@ -1720,7 +1792,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46311.0090652003</v>
+        <v>46311.01573482075</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1755,7 +1827,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -1786,7 +1862,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46311.00907385675</v>
+        <v>46311.01574335889</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1897,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -1852,7 +1932,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46311.00909378632</v>
+        <v>46311.0157518109</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -1887,7 +1967,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -1918,7 +2002,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46311.00910207501</v>
+        <v>46311.01576011192</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -1953,7 +2037,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -1984,7 +2072,7 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46311.00911054684</v>
+        <v>46311.01576842059</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -2019,7 +2107,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -2050,7 +2142,7 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46311.00911882619</v>
+        <v>46311.01577662482</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2085,7 +2177,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -2116,7 +2212,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46311.00912745361</v>
+        <v>46311.01579782196</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2151,7 +2247,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -2182,7 +2282,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46311.00913566191</v>
+        <v>46311.01580622511</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2317,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Fee €40 per player</t>
@@ -2248,7 +2352,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46311.00914401731</v>
+        <v>46311.01581450277</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2283,7 +2387,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -2314,7 +2422,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46311.00915273234</v>
+        <v>46311.01582273754</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2349,7 +2457,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -2380,7 +2492,7 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46311.00916113639</v>
+        <v>46311.01583101301</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2415,7 +2527,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>30 € per player</t>
@@ -2442,7 +2558,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46311.00916981779</v>
+        <v>46311.01583928576</v>
       </c>
       <c r="R30" s="2" t="n"/>
     </row>
@@ -2473,7 +2589,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>40€</t>
@@ -2504,7 +2624,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46311.00917870067</v>
+        <v>46311.01584743954</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2539,7 +2659,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>40 Euros per player</t>
@@ -2570,7 +2694,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46311.00918779985</v>
+        <v>46311.01585602768</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2605,7 +2729,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -2636,7 +2764,7 @@
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46311.00919654341</v>
+        <v>46311.01586447237</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -2671,7 +2799,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>40€</t>
@@ -2702,7 +2834,7 @@
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46311.00920491044</v>
+        <v>46311.01587283832</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -2737,7 +2869,11 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2900,7 @@
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46311.00921347404</v>
+        <v>46311.01588093435</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -2799,7 +2935,11 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -2826,7 +2966,7 @@
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46311.00922199796</v>
+        <v>46311.01588923248</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -2861,7 +3001,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
@@ -2892,7 +3036,7 @@
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46311.00923038685</v>
+        <v>46311.01589748889</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -2927,7 +3071,11 @@
           <t>Female/Male</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -2954,7 +3102,7 @@
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46311.009238598</v>
+        <v>46311.01590580729</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3032,7 +3180,7 @@
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46311.00925219018</v>
+        <v>46311.01591919145</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -3110,7 +3258,7 @@
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46311.00925220264</v>
+        <v>46311.0159192039</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3336,7 @@
         </is>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>46311.00925222162</v>
+        <v>46311.01591922331</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -3266,7 +3414,7 @@
         </is>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>46311.00925223475</v>
+        <v>46311.01591923639</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -3344,7 +3492,7 @@
         </is>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>46311.00925225037</v>
+        <v>46311.01591925247</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -3422,7 +3570,7 @@
         </is>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>46311.00925226259</v>
+        <v>46311.01591926477</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -3500,7 +3648,7 @@
         </is>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>46311.00925228146</v>
+        <v>46311.0159192827</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -3578,7 +3726,7 @@
         </is>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>46311.00925229386</v>
+        <v>46311.0159192951</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -3644,7 +3792,7 @@
         </is>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>46311.00925232578</v>
+        <v>46311.01591932707</v>
       </c>
       <c r="R47" s="2" t="n"/>
     </row>

--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$R$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -466,6 +466,7 @@
     <col width="23" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -559,11 +560,16 @@
           <t>Fonte do prazo</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fuso do prazo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LISBOA II</t>
+          <t>FIP PROMISES ANCONA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -573,12 +579,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -599,7 +605,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lisboa-ii/</t>
+          <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
@@ -612,7 +618,7 @@
         <v>46316</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="4" t="n"/>
@@ -622,18 +628,23 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46311.01558229799</v>
+        <v>46311.6179100348</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ANCONA</t>
+          <t>FIP PROMISES LISBOA II</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -643,12 +654,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -669,7 +680,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-lisboa-ii/</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
@@ -682,7 +693,7 @@
         <v>46316</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="4" t="n"/>
@@ -692,11 +703,16 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46311.01559053672</v>
+        <v>46311.61791871495</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -752,7 +768,7 @@
         <v>46323</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="4" t="n"/>
@@ -762,11 +778,16 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46311.01559871531</v>
+        <v>46311.61792709393</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -822,7 +843,7 @@
         <v>46323</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="4" t="n"/>
@@ -832,11 +853,16 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46311.0156069881</v>
+        <v>46311.61793536676</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -888,7 +914,7 @@
         <v>46323</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="4" t="n"/>
@@ -898,11 +924,16 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46311.01561524518</v>
+        <v>46311.61794363501</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -958,7 +989,7 @@
         <v>46330</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="4" t="n"/>
@@ -968,18 +999,23 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46311.01562376043</v>
+        <v>46311.61795247591</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ROESELARE</t>
+          <t>FIP PROMISES PERUGIA III</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -989,12 +1025,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -1015,7 +1051,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
@@ -1028,7 +1064,7 @@
         <v>46330</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="4" t="n"/>
@@ -1038,18 +1074,23 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46311.01564137753</v>
+        <v>46311.61796077184</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES PERUGIA III</t>
+          <t>FIP PROMISES ROESELARE</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1059,12 +1100,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -1085,7 +1126,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
@@ -1098,7 +1139,7 @@
         <v>46330</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="4" t="n"/>
@@ -1108,11 +1149,16 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46311.01564964397</v>
+        <v>46311.61796905485</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1210,7 @@
         <v>46330</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="4" t="n"/>
@@ -1174,18 +1220,23 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46311.01565801506</v>
+        <v>46311.61797734768</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LLEIDA</t>
+          <t>FIP PROMISES RENDE</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1195,12 +1246,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Rende</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -1214,14 +1265,10 @@
           <t>JOV</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
@@ -1234,7 +1281,7 @@
         <v>46337</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="4" t="n"/>
@@ -1244,18 +1291,23 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46311.01566629728</v>
+        <v>46311.61798558367</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES RENDE</t>
+          <t>FIP PROMISES LLEIDA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1265,12 +1317,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Rende</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -1284,10 +1336,14 @@
           <t>JOV</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
         </is>
       </c>
       <c r="J12" s="3" t="n">
@@ -1300,7 +1356,7 @@
         <v>46337</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="4" t="n"/>
@@ -1310,18 +1366,23 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46311.01567451712</v>
+        <v>46311.61799376961</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER DAMAC DUBAI II</t>
+          <t>FIP BRONZE JC FERRERO ACADEMY</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1331,12 +1392,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Villena</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -1352,12 +1413,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-damac-dubai-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-jc-ferrero-academy-2026/</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
@@ -1370,7 +1431,7 @@
         <v>46311</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="4" t="n"/>
@@ -1380,18 +1441,23 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46311.0156827271</v>
+        <v>46311.61800228213</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY PHANGAN</t>
+          <t>FIP BRONZE CYPRUS III</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1401,14 +1467,10 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Phangan</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
+          <t>Ayia Napa / Cyprus</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1422,12 +1484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€ per player</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-ko-panghan/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iii-2026/</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
@@ -1440,7 +1502,7 @@
         <v>46311</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="4" t="n"/>
@@ -1450,18 +1512,23 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46311.01569105346</v>
+        <v>46311.61801052289</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE TASHKENT</t>
+          <t>FIP SILVER DAMAC DUBAI II</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1471,12 +1538,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tashkent</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -1492,12 +1559,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-tashkent-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-damac-dubai-ii-2026/</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
@@ -1510,7 +1577,7 @@
         <v>46311</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="4" t="n"/>
@@ -1520,18 +1587,23 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46311.01569943015</v>
+        <v>46311.61801866544</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE JC FERRERO ACADEMY</t>
+          <t>FIP BRONZE HIGH VELOCITY PHANGAN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1541,12 +1613,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Villena</t>
+          <t>Phangan</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -1567,7 +1639,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-jc-ferrero-academy-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-ko-panghan/</t>
         </is>
       </c>
       <c r="J16" s="3" t="n">
@@ -1580,7 +1652,7 @@
         <v>46311</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="4" t="n"/>
@@ -1590,18 +1662,23 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46311.01570782824</v>
+        <v>46311.6180271345</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS III</t>
+          <t>FIP BRONZE TASHKENT</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1611,10 +1688,14 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ayia Napa / Cyprus</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
+          <t>Tashkent</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1628,12 +1709,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40€ per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-tashkent-2026/</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
@@ -1646,7 +1727,7 @@
         <v>46311</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="4" t="n"/>
@@ -1656,11 +1737,16 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46311.01571651395</v>
+        <v>46311.61803526987</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1802,7 @@
         <v>46311</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="4" t="n"/>
@@ -1726,18 +1812,23 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46311.0157249788</v>
+        <v>46311.6180436519</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS IV</t>
+          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1747,14 +1838,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ayia Napa / Cyprus</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1764,12 +1859,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40€ per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
       <c r="J19" s="3" t="n">
@@ -1782,7 +1877,7 @@
         <v>46318</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="4" t="n"/>
@@ -1792,18 +1887,23 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46311.01573482075</v>
+        <v>46311.61805192605</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ESC PADEL</t>
+          <t>FIP BRONZE CYPRUS IV</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1813,14 +1913,10 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Espoo</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
+          <t>Ayia Napa / Cyprus</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1834,12 +1930,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€ per player</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
@@ -1852,7 +1948,7 @@
         <v>46318</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="4" t="n"/>
@@ -1862,18 +1958,23 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46311.01574335889</v>
+        <v>46311.61806059377</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
+          <t>FIP BRONZE ESC PADEL</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1883,18 +1984,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Malé</t>
+          <t>Espoo</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1909,7 +2010,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
       <c r="J21" s="3" t="n">
@@ -1922,7 +2023,7 @@
         <v>46318</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="4" t="n"/>
@@ -1932,18 +2033,23 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46311.0157518109</v>
+        <v>46311.6180689041</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOHA II</t>
+          <t>FIP BRONZE PALA PADEL NOLA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1953,12 +2059,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Nola</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -1979,7 +2085,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-pala-padel-nola-2026/</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
@@ -1992,7 +2098,7 @@
         <v>46325</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N22" s="3" t="n"/>
       <c r="O22" s="4" t="n"/>
@@ -2002,18 +2108,23 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46311.01576011192</v>
+        <v>46311.61807817718</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE PALA PADEL NOLA</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2023,7 +2134,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nola</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2049,7 +2160,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-pala-padel-nola-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
@@ -2062,7 +2173,7 @@
         <v>46325</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="4" t="n"/>
@@ -2072,18 +2183,23 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46311.01576842059</v>
+        <v>46311.61808639285</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MEDIOLANUM COMO</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2093,18 +2209,18 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2119,7 +2235,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
@@ -2132,7 +2248,7 @@
         <v>46325</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="4" t="n"/>
@@ -2142,18 +2258,23 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46311.01577662482</v>
+        <v>46311.61809465201</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2163,18 +2284,18 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2189,7 +2310,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
@@ -2202,7 +2323,7 @@
         <v>46325</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="4" t="n"/>
@@ -2212,11 +2333,16 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46311.01579782196</v>
+        <v>46311.61810291646</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2398,7 @@
         <v>46332</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="4" t="n"/>
@@ -2282,18 +2408,23 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46311.01580622511</v>
+        <v>46311.61811140149</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER GO PARK HONG KONG</t>
+          <t>FIP BRONZE SWEDEN II</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2303,12 +2434,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Skurup</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
@@ -2324,25 +2455,25 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Fee €40 per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="4" t="n"/>
@@ -2352,18 +2483,23 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46311.01581450277</v>
+        <v>46311.618120005</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MCV PADELNESS</t>
+          <t>FIP BRONZE CHILE IX</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2373,18 +2509,18 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2394,12 +2530,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
       <c r="J28" s="3" t="n">
@@ -2408,12 +2544,8 @@
       <c r="K28" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L28" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="4" t="n"/>
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="2" t="inlineStr">
@@ -2422,18 +2554,15 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46311.01582273754</v>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>página FIP</t>
-        </is>
-      </c>
+        <v>46311.61813390671</v>
+      </c>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE SWEDEN II</t>
+          <t>FIP BRONZE KARACHI II</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2443,12 +2572,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
@@ -2464,25 +2593,25 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="4" t="n"/>
@@ -2492,18 +2621,23 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46311.01583101301</v>
+        <v>46311.61814218662</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CHILE IX</t>
+          <t>FIP BRONZE ROCHEFORT</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2513,12 +2647,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
@@ -2534,12 +2668,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
@@ -2548,8 +2682,12 @@
       <c r="K30" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="4" t="n"/>
+      <c r="L30" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="2" t="inlineStr">
@@ -2558,14 +2696,23 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46311.01583928576</v>
-      </c>
-      <c r="R30" s="2" t="n"/>
+        <v>46311.61815056158</v>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE KARACHI II</t>
+          <t>FIP BRONZE IURRETA PADELKO</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2575,12 +2722,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Iurreta</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
@@ -2596,12 +2743,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
@@ -2614,7 +2761,7 @@
         <v>46332</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="4" t="n"/>
@@ -2624,18 +2771,23 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46311.01584743954</v>
+        <v>46311.61817057968</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROCHEFORT</t>
+          <t>FIP BRONZE ACCRA – GHANA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2645,18 +2797,18 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Rochefort</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2666,12 +2818,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
       <c r="J32" s="3" t="n">
@@ -2684,7 +2836,7 @@
         <v>46332</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="4" t="n"/>
@@ -2694,18 +2846,23 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46311.01585602768</v>
+        <v>46311.61817919923</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE IURRETA PADELKO</t>
+          <t>FIP SILVER GO PARK HONG KONG</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2715,12 +2872,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Iurreta</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E33" s="2" t="n"/>
@@ -2736,12 +2893,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>Fee €40 per player</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
@@ -2754,7 +2911,7 @@
         <v>46332</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="4" t="n"/>
@@ -2764,18 +2921,23 @@
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46311.01586447237</v>
+        <v>46311.61818786939</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ACCRA – GHANA</t>
+          <t>FIP SILVER MCV PADELNESS</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2785,12 +2947,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
@@ -2806,12 +2968,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
       <c r="J34" s="3" t="n">
@@ -2824,7 +2986,7 @@
         <v>46332</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N34" s="3" t="n"/>
       <c r="O34" s="4" t="n"/>
@@ -2834,11 +2996,16 @@
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46311.01587283832</v>
+        <v>46311.61819684938</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -2890,7 +3057,7 @@
         <v>46339</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N35" s="3" t="n"/>
       <c r="O35" s="4" t="n"/>
@@ -2900,11 +3067,16 @@
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46311.01588093435</v>
+        <v>46311.61820444668</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -2956,7 +3128,7 @@
         <v>46339</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="4" t="n"/>
@@ -2966,11 +3138,16 @@
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46311.01588923248</v>
+        <v>46311.61821261773</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3203,7 @@
         <v>46339</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="4" t="n"/>
@@ -3036,11 +3213,16 @@
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46311.01589748889</v>
+        <v>46311.61822027617</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3274,7 @@
         <v>46339</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="4" t="n"/>
@@ -3102,11 +3284,16 @@
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46311.01590580729</v>
+        <v>46311.61822876071</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
@@ -3180,11 +3367,16 @@
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46311.01591919145</v>
+        <v>46311.61824210344</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3258,11 +3450,16 @@
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46311.0159192039</v>
+        <v>46311.6182421162</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3336,11 +3533,16 @@
         </is>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>46311.01591922331</v>
+        <v>46311.61824213548</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3414,11 +3616,16 @@
         </is>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>46311.01591923639</v>
+        <v>46311.61824214849</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3492,11 +3699,16 @@
         </is>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>46311.01591925247</v>
+        <v>46311.61824216414</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3570,11 +3782,16 @@
         </is>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>46311.01591926477</v>
+        <v>46311.61824217647</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3648,11 +3865,16 @@
         </is>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>46311.0159192827</v>
+        <v>46311.6182421947</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3726,11 +3948,16 @@
         </is>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>46311.0159192951</v>
+        <v>46311.61824220695</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
@@ -3792,12 +4019,13 @@
         </is>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>46311.01591932707</v>
+        <v>46311.6182422383</v>
       </c>
       <c r="R47" s="2" t="n"/>
+      <c r="S47" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R47"/>
+  <autoFilter ref="A1:S47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,13 +445,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -463,7 +463,7 @@
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46311.6179100348</v>
+        <v>46311.775057627</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46311.61791871495</v>
+        <v>46311.77506627471</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46311.61792709393</v>
+        <v>46311.77507473071</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46311.61793536676</v>
+        <v>46311.77508356074</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46311.61794363501</v>
+        <v>46311.7750921886</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46311.61795247591</v>
+        <v>46311.77510110787</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES PERUGIA III</t>
+          <t>FIP PROMISES ROESELARE</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46311.61796077184</v>
+        <v>46311.77511001324</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ROESELARE</t>
+          <t>FIP PROMISES PERUGIA III</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46311.61796905485</v>
+        <v>46311.77511874386</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46311.61797734768</v>
+        <v>46311.77512740501</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES RENDE</t>
+          <t>FIP PROMISES LLEIDA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Rende</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -1265,10 +1265,14 @@
           <t>JOV</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
@@ -1291,7 +1295,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46311.61798558367</v>
+        <v>46311.7751360054</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1307,7 +1311,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LLEIDA</t>
+          <t>FIP PROMISES RENDE</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1317,12 +1321,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Rende</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -1336,14 +1340,10 @@
           <t>JOV</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
         </is>
       </c>
       <c r="J12" s="3" t="n">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46311.61799376961</v>
+        <v>46311.77514486205</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE JC FERRERO ACADEMY</t>
+          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1392,18 +1392,18 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Villena</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-jc-ferrero-academy-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46311.61800228213</v>
+        <v>46311.77515372555</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS III</t>
+          <t>FIP BRONZE CYPRUS IV</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46311.61801052289</v>
+        <v>46311.77516229708</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER DAMAC DUBAI II</t>
+          <t>FIP BRONZE ESC PADEL</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Espoo</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -1559,22 +1559,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-damac-dubai-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46311.61801866544</v>
+        <v>46311.77517110338</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY PHANGAN</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Phangan</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -1639,17 +1639,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-ko-panghan/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>46321</v>
+        <v>46335</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46327</v>
+        <v>46341</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46311</v>
+        <v>46325</v>
       </c>
       <c r="M16" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46311.6180271345</v>
+        <v>46311.77517977246</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE TASHKENT</t>
+          <t>FIP BRONZE PALA PADEL NOLA</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Tashkent</t>
+          <t>Nola</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -1714,17 +1714,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-tashkent-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-pala-padel-nola-2026/</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>46321</v>
+        <v>46335</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46327</v>
+        <v>46341</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46311</v>
+        <v>46325</v>
       </c>
       <c r="M17" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46311.61803526987</v>
+        <v>46311.77518840483</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FIP GOLD MEDIOLANUM PADEL CUP TORINO</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1784,22 +1784,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40 €</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-gold-mediolanum-torino-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>46322</v>
+        <v>46335</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46327</v>
+        <v>46341</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>46311</v>
+        <v>46325</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46311.6180436519</v>
+        <v>46311.77519886811</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1838,18 +1838,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Malé</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1864,17 +1864,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46311.61805192605</v>
+        <v>46311.77520762284</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS IV</t>
+          <t>FIP PLATINUM AGUASCALIENTES</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1913,10 +1913,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Ayia Napa / Cyprus</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1930,22 +1934,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40€ per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
+          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>46328</v>
+        <v>46341</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>46334</v>
+        <v>46347</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46318</v>
+        <v>46332</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1958,7 +1962,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46311.61806059377</v>
+        <v>46311.77521681086</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -1974,7 +1978,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ESC PADEL</t>
+          <t>FIP SILVER MCV PADELNESS</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1984,12 +1988,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Espoo</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -2010,17 +2014,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>46328</v>
+        <v>46342</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>46334</v>
+        <v>46348</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46318</v>
+        <v>46332</v>
       </c>
       <c r="M21" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2033,7 +2037,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46311.6180689041</v>
+        <v>46311.77522549355</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2049,7 +2053,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE PALA PADEL NOLA</t>
+          <t>FIP BRONZE SWEDEN II</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2059,12 +2063,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nola</t>
+          <t>Skurup</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -2085,17 +2089,17 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-pala-padel-nola-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2108,7 +2112,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46311.61807817718</v>
+        <v>46311.77523419022</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2124,7 +2128,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MEDIOLANUM COMO</t>
+          <t>FIP BRONZE CHILE IX</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2134,18 +2138,18 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2155,26 +2159,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46341</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>46325</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46348</v>
+      </c>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="4" t="n"/>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="2" t="inlineStr">
@@ -2183,23 +2183,15 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46311.61808639285</v>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>página FIP</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Paris</t>
-        </is>
-      </c>
+        <v>46311.77524276562</v>
+      </c>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
+          <t>FIP BRONZE KARACHI II</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2209,18 +2201,18 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2230,22 +2222,22 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="M24" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2258,7 +2250,7 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46311.61809465201</v>
+        <v>46311.77525133151</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2274,7 +2266,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOHA II</t>
+          <t>FIP BRONZE ROCHEFORT</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2284,18 +2276,18 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2305,22 +2297,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2333,7 +2325,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46311.61810291646</v>
+        <v>46311.77525981468</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2349,7 +2341,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FIP PLATINUM AGUASCALIENTES</t>
+          <t>FIP BRONZE IURRETA PADELKO</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2359,12 +2351,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Aguascalientes</t>
+          <t>Iurreta</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
@@ -2385,14 +2377,14 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>46332</v>
@@ -2408,7 +2400,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46311.61811140149</v>
+        <v>46311.77526855712</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2424,7 +2416,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE SWEDEN II</t>
+          <t>FIP BRONZE ACCRA – GHANA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2434,12 +2426,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
@@ -2455,19 +2447,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>46332</v>
@@ -2483,7 +2475,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46311.618120005</v>
+        <v>46311.77527727777</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2499,7 +2491,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CHILE IX</t>
+          <t>FIP SILVER GO PARK HONG KONG</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2509,18 +2501,18 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2530,12 +2522,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>Fee €40 per player</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
       <c r="J28" s="3" t="n">
@@ -2544,8 +2536,12 @@
       <c r="K28" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="4" t="n"/>
+      <c r="L28" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="2" t="inlineStr">
@@ -2554,15 +2550,23 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46311.61813390671</v>
-      </c>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
+        <v>46311.77528586544</v>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE KARACHI II</t>
+          <t>FIP SILVER ROESELARE</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2572,18 +2576,18 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2591,24 +2595,20 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>40€</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="M29" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46311.61814218662</v>
+        <v>46311.77529468353</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROCHEFORT</t>
+          <t>FIP BRONZE ROESELARE</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Rochefort</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2666,24 +2666,20 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>40 Euros per player</t>
-        </is>
-      </c>
+      <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2696,7 +2692,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46311.61815056158</v>
+        <v>46311.77530355435</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -2712,7 +2708,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE IURRETA PADELKO</t>
+          <t>FIP BRONZE DENIA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2722,7 +2718,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Iurreta</t>
+          <t>Denia</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2748,17 +2744,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2771,7 +2767,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46311.61817057968</v>
+        <v>46311.7753122421</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2787,7 +2783,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ACCRA – GHANA</t>
+          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2797,12 +2793,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
@@ -2816,24 +2812,20 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>40€</t>
-        </is>
-      </c>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2846,7 +2838,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46311.61817919923</v>
+        <v>46311.7753211599</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2862,28 +2854,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER GO PARK HONG KONG</t>
+          <t>Open A-Z Padel Guimarães</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Top-padel Guimarães</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2893,72 +2889,80 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Fee €40 per player</t>
+          <t>Ver regulamento interno</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>46342</v>
+        <v>46316</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>46348</v>
+        <v>46320</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46332</v>
+        <v>46309</v>
       </c>
       <c r="M33" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="O33" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="4" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46311.61818786939</v>
+        <v>46311.77533509177</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>detalhe</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MCV PADELNESS</t>
+          <t>5º Open Padcenter</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Odivelas</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Padcenter Odivelas</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2968,72 +2972,80 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>Ver regulamento interno</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>46342</v>
+        <v>46317</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>46348</v>
+        <v>46320</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46332</v>
+        <v>46309</v>
       </c>
       <c r="M34" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="O34" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="4" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46311.61819684938</v>
+        <v>46311.77533510437</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>detalhe</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER ROESELARE</t>
+          <t>1º Open de Absolutos by GRIP</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Pinhal Novo</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>GRIP - Grande Indoor Padel</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3041,70 +3053,82 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>46349</v>
+        <v>46322</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>46355</v>
+        <v>46327</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46339</v>
+        <v>46315</v>
       </c>
       <c r="M35" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="O35" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="4" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46311.61820444668</v>
+        <v>46311.77533512273</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>detalhe</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROESELARE</t>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Ultra Padel Club</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3112,70 +3136,82 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>46349</v>
+        <v>46323</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>46355</v>
+        <v>46327</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>46339</v>
+        <v>46315</v>
       </c>
       <c r="M36" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="O36" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N36" s="3" t="n"/>
-      <c r="O36" s="4" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46311.61821261773</v>
+        <v>46311.77533513511</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>detalhe</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DENIA</t>
+          <t>Open Luximos Christie's 2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Denia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Your Top-padel Industrial</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3185,72 +3221,80 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>Ver regulamento interno</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>46349</v>
+        <v>46325</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>46355</v>
+        <v>46327</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>46339</v>
+        <v>46315</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="4" t="n"/>
+        <v>0.625</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46311.61822027617</v>
+        <v>46311.7753351508</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>detalhe</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
+          <t>III Open W Padel &amp; Ténis Parque</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>W Padel Ténis &amp; Parque</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3258,49 +3302,57 @@
           <t>ABS</t>
         </is>
       </c>
-      <c r="H38" s="2" t="n"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>46349</v>
+        <v>46325</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>46355</v>
+        <v>46327</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46339</v>
+        <v>46316</v>
       </c>
       <c r="M38" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="O38" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N38" s="3" t="n"/>
-      <c r="O38" s="4" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46311.61822876071</v>
+        <v>46311.77533516366</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>detalhe</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Open A-Z Padel Guimarães</t>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3310,7 +3362,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3320,7 +3372,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Top-padel Guimarães</t>
+          <t>Dezporvinte</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3340,34 +3392,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>46316</v>
+        <v>46332</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46320</v>
+        <v>46334</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46309</v>
+        <v>46322</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46311</v>
+        <v>46324</v>
       </c>
       <c r="O39" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46311.61824210344</v>
+        <v>46311.77533518152</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -3383,7 +3435,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>5º Open Padcenter</t>
+          <t>Open Caetano Auto</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3393,7 +3445,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Odivelas</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3403,7 +3455,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Padcenter Odivelas</t>
+          <t>Quinta de Monserrate Gaia</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3423,34 +3475,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenCaetano26</t>
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>46317</v>
+        <v>46332</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46320</v>
+        <v>46334</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>46309</v>
+        <v>46322</v>
       </c>
       <c r="M40" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>46311</v>
+        <v>46324</v>
       </c>
       <c r="O40" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46311.6182421162</v>
+        <v>46311.77533519365</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3466,7 +3518,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos by GRIP</t>
+          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3476,7 +3528,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3486,19 +3538,15 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>GRIP - Grande Indoor Padel</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
+          <t>M &amp; F</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -3506,526 +3554,32 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>46322</v>
+        <v>46345</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>46317</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46348</v>
+      </c>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="4" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>46311.61824213548</v>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Leiria</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Ultra Padel Club</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>46323</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições abertas</t>
-        </is>
-      </c>
-      <c r="Q42" s="5" t="n">
-        <v>46311.61824214849</v>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Open Luximos Christie's 2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Your Top-padel Industrial</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>46325</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>46317</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições abertas</t>
-        </is>
-      </c>
-      <c r="Q43" s="5" t="n">
-        <v>46311.61824216414</v>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Barreiro</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>W Padel Ténis &amp; Parque</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>46325</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>46316</v>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="O44" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições abertas</t>
-        </is>
-      </c>
-      <c r="Q44" s="5" t="n">
-        <v>46311.61824217647</v>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Santarém</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Dezporvinte</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições abertas</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="n">
-        <v>46311.6182421947</v>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Open Caetano Auto</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Vila Nova de Gaia</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Quinta de Monserrate Gaia</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenCaetano26</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições abertas</t>
-        </is>
-      </c>
-      <c r="Q46" s="5" t="n">
-        <v>46311.61824220695</v>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>M &amp; F</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>46345</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="3" t="n"/>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições fechadas</t>
-        </is>
-      </c>
-      <c r="Q47" s="5" t="n">
-        <v>46311.6182422383</v>
-      </c>
-      <c r="R47" s="2" t="n"/>
-      <c r="S47" s="2" t="n"/>
+        <v>46311.77533522629</v>
+      </c>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S47"/>
+  <autoFilter ref="A1:S41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46311.775057627</v>
+        <v>46311.77793234788</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46311.77506627471</v>
+        <v>46311.77794107998</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46311.77507473071</v>
+        <v>46311.77794981119</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46311.77508356074</v>
+        <v>46311.77795864822</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46311.7750921886</v>
+        <v>46311.77796742376</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46311.77510110787</v>
+        <v>46311.77797664765</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46311.77511001324</v>
+        <v>46311.7779854401</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46311.77511874386</v>
+        <v>46311.77799422638</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46311.77512740501</v>
+        <v>46311.7780029065</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46311.7751360054</v>
+        <v>46311.77801148154</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46311.77514486205</v>
+        <v>46311.77802034446</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46311.77515372555</v>
+        <v>46311.7780292532</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46311.77516229708</v>
+        <v>46311.7780381969</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46311.77517110338</v>
+        <v>46311.77804696791</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46311.77517977246</v>
+        <v>46311.7780558763</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46311.77518840483</v>
+        <v>46311.77806468696</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46311.77519886811</v>
+        <v>46311.77807373724</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46311.77520762284</v>
+        <v>46311.77808246924</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46311.77521681086</v>
+        <v>46311.77809163814</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46311.77522549355</v>
+        <v>46311.77810008163</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46311.77523419022</v>
+        <v>46311.77810868285</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46311.77524276562</v>
+        <v>46311.77811726721</v>
       </c>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46311.77525133151</v>
+        <v>46311.77812620834</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46311.77525981468</v>
+        <v>46311.77813499569</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46311.77526855712</v>
+        <v>46311.7781436307</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46311.77527727777</v>
+        <v>46311.77815366491</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46311.77528586544</v>
+        <v>46311.77816253708</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46311.77529468353</v>
+        <v>46311.77817128984</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46311.77530355435</v>
+        <v>46311.77818202328</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46311.7753122421</v>
+        <v>46311.77819100332</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46311.7753211599</v>
+        <v>46311.77820003036</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Open A-Z Padel Guimarães</t>
+          <t>Campeonato Nacional Veterano</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2874,19 +2874,15 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Top-padel Guimarães</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>ABS</t>
-        </is>
-      </c>
+          <t>F &amp; M: +35, +40, +45, +50, +55, +60</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -2894,50 +2890,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+          <t>https://fpp.tiepadel.com/tournaments/HeyDocNacionalVeteranos2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>46316</v>
+        <v>46311</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>46320</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>46309</v>
-      </c>
-      <c r="M33" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="O33" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46313</v>
+      </c>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="4" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Torneio a decorrer</t>
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46311.77533509177</v>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+        <v>46311.77821406424</v>
+      </c>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>5º Open Padcenter</t>
+          <t>Open A-Z Padel Guimarães</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2947,7 +2927,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Odivelas</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2957,7 +2937,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Padcenter Odivelas</t>
+          <t>Top-padel Guimarães</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2977,11 +2957,11 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>46320</v>
@@ -3004,7 +2984,7 @@
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46311.77533510437</v>
+        <v>46311.77821408331</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -3020,7 +3000,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos by GRIP</t>
+          <t>5º Open Padcenter</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3030,7 +3010,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Odivelas</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3040,7 +3020,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>GRIP - Grande Indoor Padel</t>
+          <t>Padcenter Odivelas</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3060,34 +3040,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>46327</v>
+        <v>46320</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46315</v>
+        <v>46309</v>
       </c>
       <c r="M35" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46317</v>
+        <v>46311</v>
       </c>
       <c r="O35" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46311.77533512273</v>
+        <v>46311.77821409639</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -3103,7 +3083,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
+          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3113,7 +3093,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Pinhal Novo</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3123,7 +3103,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Ultra Padel Club</t>
+          <t>GRIP - Grande Indoor Padel</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3143,11 +3123,11 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>46327</v>
@@ -3159,7 +3139,7 @@
         <v>0.625</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="O36" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3170,7 +3150,7 @@
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46311.77533513511</v>
+        <v>46311.77821411561</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -3186,7 +3166,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Open Luximos Christie's 2026</t>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3196,7 +3176,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3206,7 +3186,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Your Top-padel Industrial</t>
+          <t>Ultra Padel Club</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3226,11 +3206,11 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>46327</v>
@@ -3242,10 +3222,10 @@
         <v>0.625</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3253,7 +3233,7 @@
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46311.7753351508</v>
+        <v>46311.77821412872</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -3269,7 +3249,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
+          <t>Open Luximos Christie's 2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3279,7 +3259,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3289,7 +3269,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>W Padel Ténis &amp; Parque</t>
+          <t>Your Top-padel Industrial</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3309,7 +3289,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
         </is>
       </c>
       <c r="J38" s="3" t="n">
@@ -3319,16 +3299,16 @@
         <v>46327</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3336,7 +3316,7 @@
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46311.77533516366</v>
+        <v>46311.77821414526</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3352,7 +3332,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+          <t>III Open W Padel &amp; Ténis Parque</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3362,7 +3342,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3372,7 +3352,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Dezporvinte</t>
+          <t>W Padel Ténis &amp; Parque</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3392,23 +3372,23 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46324</v>
+        <v>46318</v>
       </c>
       <c r="O39" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3419,7 +3399,7 @@
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46311.77533518152</v>
+        <v>46311.77821415827</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -3435,7 +3415,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Open Caetano Auto</t>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3445,7 +3425,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3455,7 +3435,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Monserrate Gaia</t>
+          <t>Dezporvinte</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3475,7 +3455,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenCaetano26</t>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
         </is>
       </c>
       <c r="J40" s="3" t="n">
@@ -3502,7 +3482,7 @@
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46311.77533519365</v>
+        <v>46311.77821417766</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3518,68 +3498,151 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>Open Caetano Auto</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Quinta de Monserrate Gaia</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>46311.77821419118</v>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>FPP Portugal</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>FPP</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>M &amp; F</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="J42" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K42" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="4" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="4" t="n"/>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="3" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>Inscrições fechadas</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="n">
-        <v>46311.77533522629</v>
-      </c>
-      <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="n"/>
+      <c r="Q42" s="5" t="n">
+        <v>46311.77821422258</v>
+      </c>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S41"/>
+  <autoFilter ref="A1:S42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -449,7 +449,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
@@ -574,7 +574,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46311.77793234788</v>
+        <v>46311.78566553765</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46311.77794107998</v>
+        <v>46311.785674334</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46311.77794981119</v>
+        <v>46311.78568300631</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46311.77795864822</v>
+        <v>46311.78569158445</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46311.77796742376</v>
+        <v>46311.78570009986</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46311.77797664765</v>
+        <v>46311.78570928227</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46311.7779854401</v>
+        <v>46311.78571803492</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46311.77799422638</v>
+        <v>46311.78572697657</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H10" s="2" t="n"/>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46311.7780029065</v>
+        <v>46311.78573553017</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46311.77801148154</v>
+        <v>46311.78574436461</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>FIP Promises</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46311.77802034446</v>
+        <v>46311.78575289779</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1382,43 +1382,39 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
+          <t>FIP BRONZE CYPRUS IV</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Malé</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
+          <t>Ayia Napa / Cyprus</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€ per player</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
@@ -1441,7 +1437,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46311.7780292532</v>
+        <v>46311.78576162203</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1457,20 +1453,24 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS IV</t>
+          <t>FIP BRONZE ESC PADEL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ayia Napa / Cyprus</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1479,17 +1479,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40€ per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46311.7780381969</v>
+        <v>46311.78577036886</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1528,33 +1528,33 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ESC PADEL</t>
+          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Espoo</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46311.77804696791</v>
+        <v>46311.78577924099</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46311.7780558763</v>
+        <v>46311.78578816544</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46311.77806468696</v>
+        <v>46311.78579725729</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46311.77807373724</v>
+        <v>46311.78580660249</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46311.77808246924</v>
+        <v>46311.78581537482</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46311.77809163814</v>
+        <v>46311.78582464443</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -1978,22 +1978,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MCV PADELNESS</t>
+          <t>FIP SILVER GO PARK HONG KONG</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -2004,17 +2004,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>Fee €40 per player</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
       <c r="J21" s="3" t="n">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46311.77810008163</v>
+        <v>46311.78583341565</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2053,22 +2053,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE SWEDEN II</t>
+          <t>FIP SILVER MCV PADELNESS</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2089,14 +2089,14 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>46332</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46311.77810868285</v>
+        <v>46311.78584236331</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2128,53 +2128,57 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CHILE IX</t>
+          <t>FIP BRONZE SWEDEN II</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Skurup</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="4" t="n"/>
+        <v>46347</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="2" t="inlineStr">
@@ -2183,51 +2187,59 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46311.77811726721</v>
-      </c>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
+        <v>46311.78585137222</v>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE KARACHI II</t>
+          <t>FIP BRONZE CHILE IX</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
@@ -2236,12 +2248,8 @@
       <c r="K24" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L24" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="4" t="n"/>
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="2" t="inlineStr">
@@ -2250,59 +2258,51 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46311.77812620834</v>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>página FIP</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Paris</t>
-        </is>
-      </c>
+        <v>46311.78586028553</v>
+      </c>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROCHEFORT</t>
+          <t>FIP BRONZE KARACHI II</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Rochefort</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46311.77813499569</v>
+        <v>46311.78586928358</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2341,43 +2341,43 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE IURRETA PADELKO</t>
+          <t>FIP BRONZE ROCHEFORT</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Iurreta</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46311.7781436307</v>
+        <v>46311.78587828794</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2416,22 +2416,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ACCRA – GHANA</t>
+          <t>FIP BRONZE IURRETA PADELKO</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Iurreta</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
@@ -2442,17 +2442,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46311.77815366491</v>
+        <v>46311.78588726227</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2491,22 +2491,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER GO PARK HONG KONG</t>
+          <t>FIP BRONZE ACCRA – GHANA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
@@ -2517,17 +2517,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Fee €40 per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
       <c r="J28" s="3" t="n">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46311.77816253708</v>
+        <v>46311.78589628095</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H29" s="2" t="n"/>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46311.77817128984</v>
+        <v>46311.78590549062</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H30" s="2" t="n"/>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46311.77818202328</v>
+        <v>46311.78591445861</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46311.77819100332</v>
+        <v>46311.78592361726</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CUPRA FIP Tour</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H32" s="2" t="n"/>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46311.77820003036</v>
+        <v>46311.78593258006</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46311.77821406424</v>
+        <v>46311.78594635036</v>
       </c>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46311.77821408331</v>
+        <v>46311.7859463703</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46311.77821409639</v>
+        <v>46311.7859463839</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46311.77821411561</v>
+        <v>46311.78594640368</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46311.77821412872</v>
+        <v>46311.78594641761</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46311.77821414526</v>
+        <v>46311.78594643412</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46311.77821415827</v>
+        <v>46311.78594644673</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46311.77821417766</v>
+        <v>46311.78594646494</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>46311.77821419118</v>
+        <v>46311.78594647784</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>46311.77821422258</v>
+        <v>46311.78594650764</v>
       </c>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>

--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,13 +445,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="37" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -569,7 +569,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ANCONA</t>
+          <t>FIP PROMISES LISBOA II</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-lisboa-ii/</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46311.78566553765</v>
+        <v>46315.35752705549</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LISBOA II</t>
+          <t>FIP PROMISES ANCONA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Ancona</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lisboa-ii/</t>
+          <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46311.785674334</v>
+        <v>46315.35753547629</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES GENVAL</t>
+          <t>FIP PROMISES BURRIANA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Genval</t>
+          <t>Burriana</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-valencia-2026-2/</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46311.78568300631</v>
+        <v>46315.357543795</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES BURRIANA</t>
+          <t>FIP PROMISES GENVAL</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Burriana</t>
+          <t>Genval</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-valencia-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46311.78569158445</v>
+        <v>46315.35755201412</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46311.78570009986</v>
+        <v>46315.35756033919</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46311.78570928227</v>
+        <v>46315.35756889434</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46311.78571803492</v>
+        <v>46315.35757730826</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46311.78572697657</v>
+        <v>46315.35758574076</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46311.78573553017</v>
+        <v>46315.35759391206</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46311.78574436461</v>
+        <v>46315.35760223975</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46311.78575289779</v>
+        <v>46315.3576104578</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1382,20 +1382,24 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS IV</t>
+          <t>FIP PROMISES TÖNISVORST</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ayia Napa / Cyprus</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n"/>
+          <t>Tönisvorst</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1404,30 +1408,26 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>40€ per player</t>
-        </is>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-tonisvorst/</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>46328</v>
+        <v>46359</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>46334</v>
+        <v>46362</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>46318</v>
+        <v>46344</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="4" t="n"/>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46311.78576162203</v>
+        <v>46315.3576187302</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1453,22 +1453,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ESC PADEL</t>
+          <t>FIP PROMISES EL PRAT DE LLOBREGAT II</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Espoo</t>
+          <t>El Prat de Llobregat</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -1479,30 +1479,30 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-el-prat-de-llobregat-ii-2026/</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>46328</v>
+        <v>46359</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46334</v>
+        <v>46362</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>46318</v>
+        <v>46344</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="4" t="n"/>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46311.78577036886</v>
+        <v>46315.3576284809</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1528,56 +1528,52 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
+          <t>FIP PROMISES MOUNTAIN VIEW</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Malé</t>
+          <t>Mountain View</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Cairo Egypt</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>40 € per player</t>
-        </is>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-mountain-view/</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>46328</v>
+        <v>46359</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46334</v>
+        <v>46362</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>46318</v>
+        <v>46344</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="4" t="n"/>
@@ -1587,7 +1583,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46311.78577924099</v>
+        <v>46315.35763677909</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1603,22 +1599,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOHA II</t>
+          <t>FIP PROMISES VILNIUS</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>Promise</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -1629,30 +1625,30 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-promises-vilnius/</t>
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>46335</v>
+        <v>46359</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46341</v>
+        <v>46362</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46325</v>
+        <v>46344</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="4" t="n"/>
@@ -1662,7 +1658,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46311.78578816544</v>
+        <v>46315.35764519506</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1678,7 +1674,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE PALA PADEL NOLA</t>
+          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1688,18 +1684,18 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nola</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1714,17 +1710,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-pala-padel-nola-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46341</v>
+        <v>46334</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="M17" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1737,7 +1733,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46311.78579725729</v>
+        <v>46315.35765340904</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1753,7 +1749,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MEDIOLANUM COMO</t>
+          <t>FIP BRONZE CYPRUS IV</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1763,14 +1759,10 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
+          <t>Ayia Napa / Cyprus</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1784,22 +1776,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€ per player</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46341</v>
+        <v>46334</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1812,7 +1804,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46311.78580660249</v>
+        <v>46315.35766176454</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1828,7 +1820,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
+          <t>FIP BRONZE ESC PADEL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1838,18 +1830,18 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Espoo</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1864,17 +1856,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>46335</v>
+        <v>46328</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46341</v>
+        <v>46334</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1887,7 +1879,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46311.78581537482</v>
+        <v>46315.35767007199</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1895,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FIP PLATINUM AGUASCALIENTES</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1913,12 +1905,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Aguascalientes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -1939,17 +1931,17 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="K20" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>46347</v>
-      </c>
       <c r="L20" s="3" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1962,7 +1954,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46311.78582464443</v>
+        <v>46315.35767831764</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -1978,7 +1970,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER GO PARK HONG KONG</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1988,18 +1980,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2009,22 +2001,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Fee €40 per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>46348</v>
+        <v>46341</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="M21" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2037,7 +2029,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46311.78583341565</v>
+        <v>46315.35768689909</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2053,7 +2045,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MCV PADELNESS</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2063,12 +2055,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -2089,17 +2081,17 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46348</v>
+        <v>46341</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2112,7 +2104,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46311.78584236331</v>
+        <v>46315.35769528168</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2120,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE SWEDEN II</t>
+          <t>FIP BRONZE LEVANTE</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2138,12 +2130,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Nola</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -2164,17 +2156,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-levante-2026/</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>46342</v>
+        <v>46335</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="M23" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2187,7 +2179,7 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46311.78585137222</v>
+        <v>46315.35770354609</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -2203,7 +2195,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CHILE IX</t>
+          <t>FIP PLATINUM AGUASCALIENTES</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2213,18 +2205,18 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2234,22 +2226,26 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="4" t="n"/>
+        <v>46347</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="2" t="inlineStr">
@@ -2258,15 +2254,23 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46311.78586028553</v>
-      </c>
-      <c r="R24" s="2" t="n"/>
-      <c r="S24" s="2" t="n"/>
+        <v>46315.35771187716</v>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE KARACHI II</t>
+          <t>FIP BRONZE ACCRA – GHANA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2276,12 +2280,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
@@ -2302,7 +2306,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
@@ -2325,7 +2329,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46311.78586928358</v>
+        <v>46315.35772026869</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2341,7 +2345,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROCHEFORT</t>
+          <t>FIP SILVER GO PARK HONG KONG</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2351,18 +2355,18 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Rochefort</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2372,12 +2376,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>Fee €40 per player</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
@@ -2400,7 +2404,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46311.78587828794</v>
+        <v>46315.35772855644</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2416,7 +2420,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE IURRETA PADELKO</t>
+          <t>FIP SILVER MCV PADELNESS</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2426,12 +2430,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Iurreta</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
@@ -2452,7 +2456,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
@@ -2475,7 +2479,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46311.78588726227</v>
+        <v>46315.3577367804</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2491,7 +2495,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ACCRA – GHANA</t>
+          <t>FIP BRONZE SWEDEN II</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2501,12 +2505,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Skurup</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
@@ -2522,19 +2526,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
       <c r="J28" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>46332</v>
@@ -2550,7 +2554,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46311.78589628095</v>
+        <v>46315.35774509856</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2566,7 +2570,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER ROESELARE</t>
+          <t>FIP BRONZE CHILE IX</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2576,12 +2580,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
@@ -2595,24 +2599,24 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>30 € per player</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>46355</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>46339</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46348</v>
+      </c>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="4" t="n"/>
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="4" t="n"/>
       <c r="P29" s="2" t="inlineStr">
@@ -2621,23 +2625,15 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46311.78590549062</v>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>página FIP</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Paris</t>
-        </is>
-      </c>
+        <v>46315.35775359478</v>
+      </c>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROESELARE</t>
+          <t>FIP BRONZE KARACHI II</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2647,18 +2643,18 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2666,20 +2662,24 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>40€</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46311.78591445861</v>
+        <v>46315.35776192202</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DENIA</t>
+          <t>FIP BRONZE ROCHEFORT</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Denia</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46311.78592361726</v>
+        <v>46315.3577703119</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
+          <t>FIP BRONZE IURRETA PADELKO</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Iurreta</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
@@ -2812,20 +2812,24 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>40 € per player</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>46349</v>
+        <v>46342</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46339</v>
+        <v>46332</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2838,7 +2842,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46311.78593258006</v>
+        <v>46315.35777877625</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2854,95 +2858,103 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Campeonato Nacional Veterano</t>
+          <t>FIP BRONZE DENIA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Denia</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>F &amp; M: +35, +40, +45, +50, +55, +60</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n"/>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/HeyDocNacionalVeteranos2026</t>
+          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>46311</v>
+        <v>46349</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>46313</v>
-      </c>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="4" t="n"/>
+        <v>46355</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Torneio a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46311.78594635036</v>
-      </c>
-      <c r="R33" s="2" t="n"/>
-      <c r="S33" s="2" t="n"/>
+        <v>46315.3577874612</v>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Open A-Z Padel Guimarães</t>
+          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Top-padel Guimarães</t>
-        </is>
-      </c>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2950,82 +2962,70 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+      <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>46316</v>
+        <v>46349</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>46320</v>
+        <v>46355</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46309</v>
+        <v>46339</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="O34" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="4" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46311.7859463703</v>
+        <v>46315.35779574317</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>detalhe</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>5º Open Padcenter</t>
+          <t>FIP SILVER ROESELARE</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Odivelas</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Padcenter Odivelas</t>
-        </is>
-      </c>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3033,82 +3033,70 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+      <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>46317</v>
+        <v>46349</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>46320</v>
+        <v>46355</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46309</v>
+        <v>46339</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="O35" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="4" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46311.7859463839</v>
+        <v>46315.35780407501</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>detalhe</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
+          <t>FIP BRONZE ROESELARE</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>GRIP - Grande Indoor Padel</t>
-        </is>
-      </c>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3116,57 +3104,49 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>46322</v>
+        <v>46349</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>46327</v>
+        <v>46355</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>46315</v>
+        <v>46339</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>46317</v>
-      </c>
-      <c r="O36" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="4" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46311.78594640368</v>
+        <v>46315.35781224772</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>detalhe</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
+          <t>Campeonato Nacional Veterano</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3176,7 +3156,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3186,19 +3166,15 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Ultra Padel Club</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
+          <t>F &amp; M: +35, +40, +45, +50, +55, +60</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -3206,50 +3182,34 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+          <t>https://fpp.tiepadel.com/tournaments/HeyDocNacionalVeteranos2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>46323</v>
+        <v>46311</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46313</v>
+      </c>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="3" t="n"/>
+      <c r="O37" s="4" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Torneio a decorrer</t>
         </is>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>46311.78594641761</v>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+        <v>46315.3578255928</v>
+      </c>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Open Luximos Christie's 2026</t>
+          <t>Open A-Z Padel Guimarães</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3259,7 +3219,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3269,7 +3229,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Your Top-padel Industrial</t>
+          <t>Top-padel Guimarães</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3289,34 +3249,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>46325</v>
+        <v>46316</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>46327</v>
+        <v>46320</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46315</v>
+        <v>46309</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>46317</v>
+        <v>46311</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>46311.78594643412</v>
+        <v>46315.3578256123</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3332,7 +3292,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
+          <t>5º Open Padcenter</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3342,7 +3302,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Odivelas</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3352,7 +3312,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>W Padel Ténis &amp; Parque</t>
+          <t>Padcenter Odivelas</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3372,34 +3332,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>46325</v>
+        <v>46317</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46327</v>
+        <v>46320</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46316</v>
+        <v>46309</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="O39" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>46311.78594644673</v>
+        <v>46315.35782562466</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -3415,7 +3375,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3425,7 +3385,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Pinhal Novo</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3435,7 +3395,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Dezporvinte</t>
+          <t>GRIP - Grande Indoor Padel</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3455,23 +3415,23 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>46332</v>
+        <v>46322</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>46322</v>
+        <v>46315</v>
       </c>
       <c r="M40" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>46324</v>
+        <v>46317</v>
       </c>
       <c r="O40" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3482,7 +3442,7 @@
         </is>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>46311.78594646494</v>
+        <v>46315.35782564314</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3498,7 +3458,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Open Caetano Auto</t>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3508,7 +3468,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3518,7 +3478,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Monserrate Gaia</t>
+          <t>Ultra Padel Club</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3538,23 +3498,23 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>46332</v>
+        <v>46323</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>46322</v>
+        <v>46315</v>
       </c>
       <c r="M41" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>46324</v>
+        <v>46318</v>
       </c>
       <c r="O41" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3565,7 +3525,7 @@
         </is>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>46311.78594647784</v>
+        <v>46315.35782565617</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -3581,68 +3541,400 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>Open Luximos Christie's 2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Your Top-padel Industrial</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>46315.35782567249</v>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>III Open W Padel &amp; Ténis Parque</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Barreiro</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>W Padel Ténis &amp; Parque</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>46315.35782568467</v>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Dezporvinte</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>46315.35782570235</v>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Open Caetano Auto</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Quinta de Monserrate Gaia</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>46315.35782571516</v>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>FPP Portugal</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>FPP</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>M &amp; F</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="J46" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K46" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="4" t="n"/>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="4" t="n"/>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>Inscrições fechadas</t>
         </is>
       </c>
-      <c r="Q42" s="5" t="n">
-        <v>46311.78594650764</v>
-      </c>
-      <c r="R42" s="2" t="n"/>
-      <c r="S42" s="2" t="n"/>
+      <c r="Q46" s="5" t="n">
+        <v>46315.35782574592</v>
+      </c>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S42"/>
+  <autoFilter ref="A1:S46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,15 +445,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -463,7 +463,7 @@
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>46315.95572164433</v>
+        <v>46315.96773327432</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>46315.95573130732</v>
+        <v>46315.96774195523</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>46315.95574064858</v>
+        <v>46315.96775058836</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>46315.95574925045</v>
+        <v>46315.96775917244</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>46315.95575966147</v>
+        <v>46315.96776766199</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>46315.95576967167</v>
+        <v>46315.96777663961</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>46315.95577925921</v>
+        <v>46315.96778530816</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>46315.9557901493</v>
+        <v>46315.96779404329</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>46315.95579983186</v>
+        <v>46315.96780263102</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>46315.95580915537</v>
+        <v>46315.96781140626</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>46315.95581860231</v>
+        <v>46315.96782513815</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>46315.95582813837</v>
+        <v>46315.96783381115</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46315.95583748475</v>
+        <v>46315.96784238909</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>46315.95584660467</v>
+        <v>46315.96785098456</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>46315.95585612921</v>
+        <v>46315.9678597004</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>46315.95586574093</v>
+        <v>46315.96786837961</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>46315.95587533167</v>
+        <v>46315.967877059</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>46315.95588411637</v>
+        <v>46315.96789789101</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>46315.95589340248</v>
+        <v>46315.96790585659</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>46315.95590312246</v>
+        <v>46315.96791510178</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>46315.95591214295</v>
+        <v>46315.96792388077</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>46315.95592148109</v>
+        <v>46315.96793277102</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>46315.95593022076</v>
+        <v>46315.96794096236</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>46315.95593955167</v>
+        <v>46315.96794988983</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>46315.95594956397</v>
+        <v>46315.96795781737</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>46315.95595877674</v>
+        <v>46315.96796703382</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>46315.95598065564</v>
+        <v>46315.9679782825</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>46315.95599003747</v>
+        <v>46315.96798712316</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>46315.95600062064</v>
+        <v>46315.96799589077</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>46315.9560098777</v>
+        <v>46315.96800500348</v>
       </c>
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>46315.95601954639</v>
+        <v>46315.96801409549</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>46315.95602962795</v>
+        <v>46315.9680231592</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>46315.95603948036</v>
+        <v>46315.96803179527</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>46315.95604903639</v>
+        <v>46315.96804052019</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>46315.95605917502</v>
+        <v>46315.96804896756</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -3143,8 +3143,802 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Open A-Z Padel Guimarães</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Guimarães</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Top-padel Guimarães</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições fechadas</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>46315.96806260775</v>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>5º Open Padcenter</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Odivelas</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Padcenter Odivelas</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições fechadas</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="n">
+        <v>46315.96806262127</v>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Pinhal Novo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>GRIP - Grande Indoor Padel</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Pagamentos a decorrer</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>46315.9680626397</v>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Ultra Padel Club</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Pagamentos a decorrer</t>
+        </is>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>46315.9680626524</v>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Open Luximos Christie's 2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Your Top-padel Industrial</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Pagamentos a decorrer</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="n">
+        <v>46315.96806266888</v>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>III Open W Padel &amp; Ténis Parque</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Barreiro</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>W Padel Ténis &amp; Parque</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>46315.96806268193</v>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Dezporvinte</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>46315.96806270065</v>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Open Caetano</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Quinta de Monserrate Gaia</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>46315.96806271408</v>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Open DL Cozinhas Míele</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>PAC - Padel Athletic Club</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="3" t="n"/>
+      <c r="O45" s="4" t="n"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>46315.96806273359</v>
+      </c>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>M &amp; F</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>46345</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="4" t="n"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições fechadas</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>46315.96806275534</v>
+      </c>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S36"/>
+  <autoFilter ref="A1:S46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$S$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -455,18 +455,19 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -507,60 +508,65 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Pontos</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Taxa de inscrição</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Link de inscrição</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Início do torneio</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Fim do torneio</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Inscrição encerra (data)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Inscrição encerra (hora)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Pagamento até (data)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Pagamento até (hora)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Status na coleta</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Coletado em</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Fonte do prazo</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Fuso do prazo</t>
         </is>
@@ -598,44 +604,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-lisboa-racket-centre-2026/</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="K2" s="3" t="n">
         <v>46331</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="L2" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>46323</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="n">
-        <v>46315.96773327432</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="5" t="n">
+        <v>46315.9695968366</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -673,44 +680,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>46331</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="n">
-        <v>46315.96774195523</v>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="5" t="n">
+        <v>46315.96960537945</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -748,44 +756,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-valencia-2026-2/</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="K4" s="3" t="n">
         <v>46338</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>46323</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="n">
-        <v>46315.96775058836</v>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="5" t="n">
+        <v>46315.96961411175</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -823,44 +832,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>46338</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>46323</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="n">
-        <v>46315.96775917244</v>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="5" t="n">
+        <v>46315.96962302219</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -899,39 +909,40 @@
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-ketameya-heights-2026/</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>46339</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="M6" s="3" t="n">
         <v>46323</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="n">
-        <v>46315.96776766199</v>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="5" t="n">
+        <v>46315.96963173385</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -969,44 +980,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-doha-iii/</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="K7" s="3" t="n">
         <v>46344</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="L7" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="M7" s="3" t="n">
         <v>46330</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="n">
-        <v>46315.96777663961</v>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="5" t="n">
+        <v>46315.96964102308</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1044,44 +1056,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="K8" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="L8" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="M8" s="3" t="n">
         <v>46330</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="n">
-        <v>46315.96778530816</v>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="5" t="n">
+        <v>46315.9696498458</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1119,44 +1132,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="K9" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>46330</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="n">
-        <v>46315.96779404329</v>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="5" t="n">
+        <v>46315.96965900504</v>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1195,39 +1209,40 @@
         </is>
       </c>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-hong-kong-v/</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>46346</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>46330</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="n">
-        <v>46315.96780263102</v>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="5" t="n">
+        <v>46315.96966816822</v>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1265,44 +1280,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="K11" s="3" t="n">
         <v>46352</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <v>46355</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>46337</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="n">
-        <v>46315.96781140626</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="5" t="n">
+        <v>46315.96967704273</v>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1341,39 +1357,40 @@
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="K12" s="3" t="n">
         <v>46352</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="L12" s="3" t="n">
         <v>46355</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="M12" s="3" t="n">
         <v>46337</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="n">
-        <v>46315.96782513815</v>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="5" t="n">
+        <v>46315.96968626617</v>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1412,39 +1429,40 @@
         </is>
       </c>
       <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-tonisvorst/</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="K13" s="3" t="n">
         <v>46359</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="L13" s="3" t="n">
         <v>46362</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="M13" s="3" t="n">
         <v>46344</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="n">
-        <v>46315.96783381115</v>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="5" t="n">
+        <v>46315.9696951369</v>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1482,44 +1500,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-el-prat-de-llobregat-ii-2026/</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="K14" s="3" t="n">
         <v>46359</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="L14" s="3" t="n">
         <v>46362</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="M14" s="3" t="n">
         <v>46344</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q14" s="5" t="n">
-        <v>46315.96784238909</v>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" s="5" t="n">
+        <v>46315.96970382436</v>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1558,39 +1577,40 @@
         </is>
       </c>
       <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-mountain-view/</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="K15" s="3" t="n">
         <v>46359</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="L15" s="3" t="n">
         <v>46362</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="M15" s="3" t="n">
         <v>46344</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="n">
-        <v>46315.96785098456</v>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" s="5" t="n">
+        <v>46315.96971277025</v>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1628,44 +1648,45 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>25€ per player/category</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-promises-vilnius/</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="K16" s="3" t="n">
         <v>46359</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="L16" s="3" t="n">
         <v>46362</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="M16" s="3" t="n">
         <v>46344</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q16" s="5" t="n">
-        <v>46315.9678597004</v>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R16" s="5" t="n">
+        <v>46315.96972153919</v>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1703,44 +1724,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="K17" s="3" t="n">
         <v>46328</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="L17" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="M17" s="3" t="n">
         <v>46318</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="N17" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="n">
-        <v>46315.96786837961</v>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" s="5" t="n">
+        <v>46315.96973053869</v>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1774,44 +1796,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>40€ per player</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="K18" s="3" t="n">
         <v>46328</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="L18" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="M18" s="3" t="n">
         <v>46318</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q18" s="5" t="n">
-        <v>46315.967877059</v>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R18" s="5" t="n">
+        <v>46315.96973968495</v>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1849,44 +1872,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>46328</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="M19" s="3" t="n">
         <v>46318</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="n">
-        <v>46315.96789789101</v>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R19" s="5" t="n">
+        <v>46315.96974856899</v>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1924,44 +1948,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-levante-2026/</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="K20" s="3" t="n">
         <v>46335</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="L20" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="M20" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="4" t="n"/>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="n">
-        <v>46315.96790585659</v>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="R20" s="5" t="n">
+        <v>46315.96975752625</v>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -1999,44 +2024,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="K21" s="3" t="n">
         <v>46335</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="L21" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="M21" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="N21" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="n">
-        <v>46315.96791510178</v>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="R21" s="5" t="n">
+        <v>46315.96976729435</v>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2074,44 +2100,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="K22" s="3" t="n">
         <v>46335</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="M22" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="N22" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q22" s="5" t="n">
-        <v>46315.96792388077</v>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="R22" s="5" t="n">
+        <v>46315.96977612662</v>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2149,44 +2176,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="K23" s="3" t="n">
         <v>46335</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="L23" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="M23" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="n">
-        <v>46315.96793277102</v>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
+      <c r="R23" s="5" t="n">
+        <v>46315.96978494665</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2224,44 +2252,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
         </is>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="K24" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="L24" s="3" t="n">
         <v>46347</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="M24" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q24" s="5" t="n">
-        <v>46315.96794096236</v>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="R24" s="5" t="n">
+        <v>46315.9697937232</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2299,44 +2328,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>40 Euros per player</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="K25" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="L25" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="M25" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="n">
-        <v>46315.96794988983</v>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="R25" s="5" t="n">
+        <v>46315.96980269321</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2374,44 +2404,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="K26" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="L26" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="M26" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="4" t="n"/>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q26" s="5" t="n">
-        <v>46315.96795781737</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R26" s="5" t="n">
+        <v>46315.96981186909</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2449,44 +2480,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>40€</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="K27" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="L27" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="M27" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="N27" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="n">
-        <v>46315.96796703382</v>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R27" s="5" t="n">
+        <v>46315.96982068669</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2524,44 +2556,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Fee €40 per player</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="K28" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="L28" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="M28" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="4" t="n"/>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q28" s="5" t="n">
-        <v>46315.9679782825</v>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R28" s="5" t="n">
+        <v>46315.96982983194</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2599,44 +2632,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="K29" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="L29" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="M29" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="4" t="n"/>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="n">
-        <v>46315.96798712316</v>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="R29" s="5" t="n">
+        <v>46315.96984264307</v>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2674,44 +2708,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="K30" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="L30" s="3" t="n">
         <v>46347</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="M30" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q30" s="5" t="n">
-        <v>46315.96799589077</v>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R30" s="5" t="n">
+        <v>46315.96985139405</v>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2749,36 +2784,37 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>30 € per player</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="K31" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="L31" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="n">
-        <v>46315.96800500348</v>
-      </c>
-      <c r="R31" s="2" t="n"/>
+      <c r="R31" s="5" t="n">
+        <v>46315.96986135008</v>
+      </c>
       <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2812,44 +2848,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>40€</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="K32" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="L32" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="M32" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q32" s="5" t="n">
-        <v>46315.96801409549</v>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
+      <c r="R32" s="5" t="n">
+        <v>46315.96987013926</v>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2888,39 +2925,40 @@
         </is>
       </c>
       <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="K33" s="3" t="n">
         <v>46349</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="L33" s="3" t="n">
         <v>46355</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="M33" s="3" t="n">
         <v>46339</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="4" t="n"/>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="n">
-        <v>46315.9680231592</v>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R33" s="5" t="n">
+        <v>46315.96987936895</v>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -2959,39 +2997,40 @@
         </is>
       </c>
       <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="K34" s="3" t="n">
         <v>46349</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="L34" s="3" t="n">
         <v>46355</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="M34" s="3" t="n">
         <v>46339</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="N34" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="n">
-        <v>46315.96803179527</v>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R34" s="5" t="n">
+        <v>46315.96988803458</v>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -3029,44 +3068,45 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>40 € per player</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="K35" s="3" t="n">
         <v>46349</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="L35" s="3" t="n">
         <v>46355</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="M35" s="3" t="n">
         <v>46339</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="4" t="n"/>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="n">
-        <v>46315.96804052019</v>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R35" s="5" t="n">
+        <v>46315.96989682173</v>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -3105,39 +3145,40 @@
         </is>
       </c>
       <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
         </is>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="K36" s="3" t="n">
         <v>46349</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="L36" s="3" t="n">
         <v>46355</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="M36" s="3" t="n">
         <v>46339</v>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="N36" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="N36" s="3" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="4" t="n"/>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>46315.96804896756</v>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
+      <c r="R36" s="5" t="n">
+        <v>46315.96990575743</v>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>página FIP</t>
         </is>
       </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>Europe/Paris</t>
         </is>
@@ -3179,48 +3220,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
         </is>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="K37" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="L37" s="3" t="n">
         <v>46320</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="M37" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="O37" s="3" t="n">
         <v>46311</v>
       </c>
-      <c r="O37" s="4" t="n">
+      <c r="P37" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="P37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>Inscrições fechadas</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="n">
-        <v>46315.96806260775</v>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
+      <c r="R37" s="5" t="n">
+        <v>46315.96991930793</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3262,48 +3306,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
         </is>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="K38" s="3" t="n">
         <v>46317</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="L38" s="3" t="n">
         <v>46320</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="M38" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="O38" s="3" t="n">
         <v>46311</v>
       </c>
-      <c r="O38" s="4" t="n">
+      <c r="P38" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="P38" s="2" t="inlineStr">
+      <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>Inscrições fechadas</t>
         </is>
       </c>
-      <c r="Q38" s="5" t="n">
-        <v>46315.96806262127</v>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
+      <c r="R38" s="5" t="n">
+        <v>46315.96991932103</v>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="T38" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3345,48 +3392,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="K39" s="3" t="n">
         <v>46322</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="L39" s="3" t="n">
         <v>46327</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="M39" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="O39" s="3" t="n">
         <v>46317</v>
       </c>
-      <c r="O39" s="4" t="n">
+      <c r="P39" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>Pagamentos a decorrer</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="n">
-        <v>46315.9680626397</v>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
+      <c r="R39" s="5" t="n">
+        <v>46315.96991934088</v>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3428,48 +3478,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="K40" s="3" t="n">
         <v>46323</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="L40" s="3" t="n">
         <v>46327</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="M40" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="O40" s="3" t="n">
         <v>46318</v>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="P40" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>Pagamentos a decorrer</t>
         </is>
       </c>
-      <c r="Q40" s="5" t="n">
-        <v>46315.9680626524</v>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
+      <c r="R40" s="5" t="n">
+        <v>46315.96991935438</v>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3511,48 +3564,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
         </is>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="K41" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="L41" s="3" t="n">
         <v>46327</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="M41" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="O41" s="3" t="n">
         <v>46317</v>
       </c>
-      <c r="O41" s="4" t="n">
+      <c r="P41" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>Pagamentos a decorrer</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="n">
-        <v>46315.96806266888</v>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R41" s="5" t="n">
+        <v>46315.96991937039</v>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3594,48 +3650,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
         </is>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="K42" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="L42" s="3" t="n">
         <v>46327</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="M42" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="O42" s="3" t="n">
         <v>46318</v>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="P42" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="P42" s="2" t="inlineStr">
+      <c r="Q42" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q42" s="5" t="n">
-        <v>46315.96806268193</v>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
+      <c r="R42" s="5" t="n">
+        <v>46315.96991938318</v>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="T42" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3677,48 +3736,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
         </is>
       </c>
-      <c r="J43" s="3" t="n">
+      <c r="K43" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="L43" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="M43" s="3" t="n">
         <v>46322</v>
       </c>
-      <c r="M43" s="4" t="n">
+      <c r="N43" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="O43" s="3" t="n">
         <v>46324</v>
       </c>
-      <c r="O43" s="4" t="n">
+      <c r="P43" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q43" s="5" t="n">
-        <v>46315.96806270065</v>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="R43" s="5" t="n">
+        <v>46315.96991940166</v>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="T43" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3760,48 +3822,51 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
         </is>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="K44" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="L44" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="M44" s="3" t="n">
         <v>46322</v>
       </c>
-      <c r="M44" s="4" t="n">
+      <c r="N44" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="O44" s="3" t="n">
         <v>46324</v>
       </c>
-      <c r="O44" s="4" t="n">
+      <c r="P44" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q44" s="5" t="n">
-        <v>46315.96806271408</v>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="R44" s="5" t="n">
+        <v>46315.96991941563</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
         <is>
           <t>detalhe</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
+      <c r="T44" s="2" t="inlineStr">
         <is>
           <t>Europe/Lisbon</t>
         </is>
@@ -3843,36 +3908,39 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
         </is>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="K45" s="3" t="n">
         <v>46335</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="L45" s="3" t="n">
         <v>46341</v>
       </c>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="4" t="n"/>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="4" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
-      <c r="Q45" s="5" t="n">
-        <v>46315.96806273359</v>
-      </c>
-      <c r="R45" s="2" t="n"/>
+      <c r="R45" s="5" t="n">
+        <v>46315.96991943593</v>
+      </c>
       <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3906,39 +3974,40 @@
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="K46" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="L46" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="4" t="n"/>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>Inscrições fechadas</t>
         </is>
       </c>
-      <c r="Q46" s="5" t="n">
-        <v>46315.96806275534</v>
-      </c>
-      <c r="R46" s="2" t="n"/>
+      <c r="R46" s="5" t="n">
+        <v>46315.96991945978</v>
+      </c>
       <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S46"/>
+  <autoFilter ref="A1:T46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="R2" s="5" t="n">
-        <v>46315.9695968366</v>
+        <v>46316.51961715194</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ANCONA</t>
+          <t>FIP PROMISES GENVAL</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ancona</t>
+          <t>Genval</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -688,17 +688,17 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-ancona-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>46331</v>
+        <v>46338</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>0.5</v>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="R3" s="5" t="n">
-        <v>46315.96960537945</v>
+        <v>46316.51962572482</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="R4" s="5" t="n">
-        <v>46315.96961411175</v>
+        <v>46316.51963438129</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES GENVAL</t>
+          <t>FIP PROMISES KETAMEYA HEIGHTS</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Genval</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -833,18 +833,14 @@
         </is>
       </c>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-ketameya-heights-2026/</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>46341</v>
@@ -863,7 +859,7 @@
         </is>
       </c>
       <c r="R5" s="5" t="n">
-        <v>46315.96962302219</v>
+        <v>46316.51964310198</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
@@ -879,7 +875,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES KETAMEYA HEIGHTS</t>
+          <t>FIP PROMISES DOHA II</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -889,12 +885,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -909,20 +905,24 @@
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-ketameya-heights-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-doha-iii/</t>
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>46339</v>
+        <v>46344</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0.5</v>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="R6" s="5" t="n">
-        <v>46315.96963173385</v>
+        <v>46316.51965178905</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES DOHA II</t>
+          <t>FIP PROMISES ROESELARE</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -988,11 +988,11 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-doha-iii/</t>
+          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>46348</v>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="R7" s="5" t="n">
-        <v>46315.96964102308</v>
+        <v>46316.51966041044</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ROESELARE</t>
+          <t>FIP PROMISES PERUGIA III</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="R8" s="5" t="n">
-        <v>46315.9696498458</v>
+        <v>46316.51966875415</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES PERUGIA III</t>
+          <t>FIP PROMISES HONG KONG V</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -1133,18 +1133,14 @@
         </is>
       </c>
       <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-hong-kong-v/</t>
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>46348</v>
@@ -1163,7 +1159,7 @@
         </is>
       </c>
       <c r="R9" s="5" t="n">
-        <v>46315.96965900504</v>
+        <v>46316.51967716745</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
@@ -1179,7 +1175,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES HONG KONG V</t>
+          <t>FIP PROMISES LLEIDA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1189,12 +1185,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
@@ -1209,20 +1205,24 @@
         </is>
       </c>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-hong-kong-v/</t>
+          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>46346</v>
+        <v>46352</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>46330</v>
+        <v>46337</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0.5</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="R10" s="5" t="n">
-        <v>46315.96966816822</v>
+        <v>46316.51968584171</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LLEIDA</t>
+          <t>FIP PROMISES RENDE</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Rende</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -1281,14 +1281,10 @@
         </is>
       </c>
       <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
@@ -1311,7 +1307,7 @@
         </is>
       </c>
       <c r="R11" s="5" t="n">
-        <v>46315.96967704273</v>
+        <v>46316.51969449667</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1323,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES RENDE</t>
+          <t>FIP PROMISES VILNIUS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1337,12 +1333,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Rende</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -1357,20 +1353,24 @@
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-vilnius/</t>
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46352</v>
+        <v>46359</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>46355</v>
+        <v>46362</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>46337</v>
+        <v>46344</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0.5</v>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="R12" s="5" t="n">
-        <v>46315.96968626617</v>
+        <v>46316.51970290064</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="R13" s="5" t="n">
-        <v>46315.9696951369</v>
+        <v>46316.51971145446</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="R14" s="5" t="n">
-        <v>46315.96970382436</v>
+        <v>46316.51972025977</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="R15" s="5" t="n">
-        <v>46315.96971277025</v>
+        <v>46316.51972876854</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
@@ -1619,57 +1619,57 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES VILNIUS</t>
+          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Promises</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25€ per player/category</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-vilnius/</t>
+          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46359</v>
+        <v>46328</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46362</v>
+        <v>46334</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>46344</v>
+        <v>46318</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="O16" s="3" t="n"/>
       <c r="P16" s="4" t="n"/>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="R16" s="5" t="n">
-        <v>46315.96972153919</v>
+        <v>46316.51973746283</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
+          <t>FIP BRONZE CYPRUS IV</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1705,18 +1705,14 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Malé</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Maldives</t>
-        </is>
-      </c>
+          <t>Ayia Napa / Cyprus</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1727,12 +1723,12 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€ per player</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -1755,7 +1751,7 @@
         </is>
       </c>
       <c r="R17" s="5" t="n">
-        <v>46315.96973053869</v>
+        <v>46316.5197459172</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1767,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS IV</t>
+          <t>FIP BRONZE ESC PADEL</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1781,10 +1777,14 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ayia Napa / Cyprus</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1799,12 +1799,12 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40€ per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>46315.96973968495</v>
+        <v>46316.51975451063</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ESC PADEL</t>
+          <t>FIP BRONZE LEVANTE</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Espoo</t>
+          <t>Nola</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -1880,17 +1880,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-levante-2026/</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="R19" s="5" t="n">
-        <v>46315.96974856899</v>
+        <v>46316.51976307976</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE LEVANTE</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nola</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-levante-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="R20" s="5" t="n">
-        <v>46315.96975752625</v>
+        <v>46316.51977187976</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MEDIOLANUM COMO</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2005,18 +2005,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
       <c r="K21" s="3" t="n">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="R21" s="5" t="n">
-        <v>46315.96976729435</v>
+        <v>46316.51978104881</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2081,18 +2081,18 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="R22" s="5" t="n">
-        <v>46315.96977612662</v>
+        <v>46316.51978954738</v>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOHA II</t>
+          <t>FIP PLATINUM AGUASCALIENTES</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -2184,17 +2184,17 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46335</v>
+        <v>46341</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="R23" s="5" t="n">
-        <v>46315.96978494665</v>
+        <v>46316.51979796115</v>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP PLATINUM AGUASCALIENTES</t>
+          <t>FIP SILVER MCV PADELNESS</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Aguascalientes</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
@@ -2260,14 +2260,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>46332</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="R24" s="5" t="n">
-        <v>46315.9697937232</v>
+        <v>46316.51980648647</v>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROCHEFORT</t>
+          <t>FIP BRONZE SWEDEN II</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2309,18 +2309,18 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Rochefort</t>
+          <t>Skurup</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2331,19 +2331,19 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>46332</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="R25" s="5" t="n">
-        <v>46315.96980269321</v>
+        <v>46316.51981506729</v>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE IURRETA PADELKO</t>
+          <t>FIP BRONZE CHILE IX</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2385,18 +2385,18 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Iurreta</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
@@ -2421,12 +2421,8 @@
       <c r="L26" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="4" t="n"/>
       <c r="O26" s="3" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="2" t="inlineStr">
@@ -2435,23 +2431,15 @@
         </is>
       </c>
       <c r="R26" s="5" t="n">
-        <v>46315.96981186909</v>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>página FIP</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Paris</t>
-        </is>
-      </c>
+        <v>46316.51982378155</v>
+      </c>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ACCRA – GHANA</t>
+          <t>FIP BRONZE KARACHI II</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2461,12 +2449,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
@@ -2488,7 +2476,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
@@ -2511,7 +2499,7 @@
         </is>
       </c>
       <c r="R27" s="5" t="n">
-        <v>46315.96982068669</v>
+        <v>46316.51983223663</v>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
@@ -2527,7 +2515,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER GO PARK HONG KONG</t>
+          <t>FIP BRONZE ROCHEFORT</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2537,18 +2525,18 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2559,12 +2547,12 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Fee €40 per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
       <c r="K28" s="3" t="n">
@@ -2587,7 +2575,7 @@
         </is>
       </c>
       <c r="R28" s="5" t="n">
-        <v>46315.96982983194</v>
+        <v>46316.51984064467</v>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
@@ -2603,7 +2591,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MCV PADELNESS</t>
+          <t>FIP BRONZE IURRETA PADELKO</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2613,12 +2601,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Iurreta</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
@@ -2640,7 +2628,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
@@ -2663,7 +2651,7 @@
         </is>
       </c>
       <c r="R29" s="5" t="n">
-        <v>46315.96984264307</v>
+        <v>46316.51984940693</v>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
@@ -2679,7 +2667,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE SWEDEN II</t>
+          <t>FIP BRONZE ACCRA – GHANA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2689,12 +2677,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
@@ -2711,19 +2699,19 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>46332</v>
@@ -2739,7 +2727,7 @@
         </is>
       </c>
       <c r="R30" s="5" t="n">
-        <v>46315.96985139405</v>
+        <v>46316.51985796809</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2743,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CHILE IX</t>
+          <t>FIP SILVER GO PARK HONG KONG</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2765,18 +2753,18 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2787,12 +2775,12 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>Fee €40 per player</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -2801,8 +2789,12 @@
       <c r="L31" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="4" t="n"/>
+      <c r="M31" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O31" s="3" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="2" t="inlineStr">
@@ -2811,15 +2803,23 @@
         </is>
       </c>
       <c r="R31" s="5" t="n">
-        <v>46315.96986135008</v>
-      </c>
-      <c r="S31" s="2" t="n"/>
-      <c r="T31" s="2" t="n"/>
+        <v>46316.51986672306</v>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE KARACHI II</t>
+          <t>FIP SILVER ROESELARE</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2829,18 +2829,18 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2849,24 +2849,20 @@
         </is>
       </c>
       <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>40€</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2879,7 +2875,7 @@
         </is>
       </c>
       <c r="R32" s="5" t="n">
-        <v>46315.96987013926</v>
+        <v>46316.51987525797</v>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
@@ -2895,7 +2891,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER ROESELARE</t>
+          <t>FIP BRONZE ROESELARE</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2916,7 +2912,7 @@
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2928,7 +2924,7 @@
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
         </is>
       </c>
       <c r="K33" s="3" t="n">
@@ -2951,7 +2947,7 @@
         </is>
       </c>
       <c r="R33" s="5" t="n">
-        <v>46315.96987936895</v>
+        <v>46316.51988432642</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
@@ -2967,7 +2963,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROESELARE</t>
+          <t>FIP BRONZE DENIA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2977,18 +2973,18 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Denia</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2997,10 +2993,14 @@
         </is>
       </c>
       <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>40 € per player</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
         </is>
       </c>
       <c r="K34" s="3" t="n">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="R34" s="5" t="n">
-        <v>46315.96988803458</v>
+        <v>46316.51989256039</v>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DENIA</t>
+          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Denia</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="E35" s="2" t="n"/>
@@ -3069,14 +3069,10 @@
         </is>
       </c>
       <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>40 € per player</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
@@ -3099,7 +3095,7 @@
         </is>
       </c>
       <c r="R35" s="5" t="n">
-        <v>46315.96989682173</v>
+        <v>46316.51990121895</v>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
@@ -3115,28 +3111,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
+          <t>Open A-Z Padel Guimarães</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Top-padel Guimarães</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3144,50 +3144,60 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="H36" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>46349</v>
+        <v>46316</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>46355</v>
+        <v>46320</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>46339</v>
+        <v>46309</v>
       </c>
       <c r="N36" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="P36" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O36" s="3" t="n"/>
-      <c r="P36" s="4" t="n"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="R36" s="5" t="n">
-        <v>46315.96990575743</v>
+        <v>46316.51991461811</v>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>detalhe</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Open A-Z Padel Guimarães</t>
+          <t>5º Open Padcenter</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3197,7 +3207,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Odivelas</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3207,7 +3217,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Top-padel Guimarães</t>
+          <t>Padcenter Odivelas</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3230,11 +3240,11 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>46320</v>
@@ -3257,7 +3267,7 @@
         </is>
       </c>
       <c r="R37" s="5" t="n">
-        <v>46315.96991930793</v>
+        <v>46316.51991463084</v>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
@@ -3273,7 +3283,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>5º Open Padcenter</t>
+          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3283,7 +3293,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Odivelas</t>
+          <t>Pinhal Novo</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3293,7 +3303,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Padcenter Odivelas</t>
+          <t>GRIP - Grande Indoor Padel</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3307,7 +3317,7 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -3316,34 +3326,34 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Pagamentos a decorrer</t>
         </is>
       </c>
       <c r="R38" s="5" t="n">
-        <v>46315.96991932103</v>
+        <v>46316.51991465061</v>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
@@ -3359,7 +3369,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3369,7 +3379,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3379,7 +3389,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>GRIP - Grande Indoor Padel</t>
+          <t>Ultra Padel Club</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3393,7 +3403,7 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -3402,11 +3412,11 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>46327</v>
@@ -3418,7 +3428,7 @@
         <v>0.625</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3429,7 +3439,7 @@
         </is>
       </c>
       <c r="R39" s="5" t="n">
-        <v>46315.96991934088</v>
+        <v>46316.51991466397</v>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
@@ -3445,7 +3455,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
+          <t>Open Luximos Christie's 2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3455,7 +3465,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3465,7 +3475,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Ultra Padel Club</t>
+          <t>Your Top-padel Industrial</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3479,7 +3489,7 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -3488,11 +3498,11 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>46327</v>
@@ -3504,10 +3514,10 @@
         <v>0.625</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
@@ -3515,7 +3525,7 @@
         </is>
       </c>
       <c r="R40" s="5" t="n">
-        <v>46315.96991935438</v>
+        <v>46316.51991468055</v>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
@@ -3531,7 +3541,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Open Luximos Christie's 2026</t>
+          <t>III Open W Padel &amp; Ténis Parque</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3541,7 +3551,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3551,7 +3561,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Your Top-padel Industrial</t>
+          <t>W Padel Ténis &amp; Parque</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3565,7 +3575,7 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -3574,7 +3584,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
@@ -3584,24 +3594,24 @@
         <v>46327</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R41" s="5" t="n">
-        <v>46315.96991937039</v>
+        <v>46316.51991469382</v>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
@@ -3617,7 +3627,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3627,7 +3637,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3637,7 +3647,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>W Padel Ténis &amp; Parque</t>
+          <t>Dezporvinte</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3651,7 +3661,7 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3660,23 +3670,23 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3687,7 +3697,7 @@
         </is>
       </c>
       <c r="R42" s="5" t="n">
-        <v>46315.96991938318</v>
+        <v>46316.51991471186</v>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
@@ -3703,7 +3713,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+          <t>Open Caetano</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3713,7 +3723,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3723,7 +3733,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Dezporvinte</t>
+          <t>Quinta de Monserrate Gaia</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3737,7 +3747,7 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -3746,7 +3756,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
         </is>
       </c>
       <c r="K43" s="3" t="n">
@@ -3773,7 +3783,7 @@
         </is>
       </c>
       <c r="R43" s="5" t="n">
-        <v>46315.96991940166</v>
+        <v>46316.51991472463</v>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3799,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Open Caetano</t>
+          <t>Open DL Cozinhas Míele</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3799,7 +3809,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3809,7 +3819,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Monserrate Gaia</t>
+          <t>PAC - Padel Athletic Club</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3823,7 +3833,7 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -3832,50 +3842,34 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>46332</v>
+        <v>46335</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46341</v>
+      </c>
+      <c r="M44" s="3" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="4" t="n"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R44" s="5" t="n">
-        <v>46315.96991941563</v>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+        <v>46316.5199147454</v>
+      </c>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Open DL Cozinhas Míele</t>
+          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3895,22 +3889,16 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>PAC - Padel Athletic Club</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>M &amp; F</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -3918,14 +3906,14 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
+          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>46335</v>
+        <v>46345</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="M45" s="3" t="n"/>
       <c r="N45" s="4" t="n"/>
@@ -3933,81 +3921,17 @@
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="R45" s="5" t="n">
-        <v>46315.96991943593</v>
+        <v>46316.51991477024</v>
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>M &amp; F</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>46345</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="4" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="4" t="n"/>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições fechadas</t>
-        </is>
-      </c>
-      <c r="R46" s="5" t="n">
-        <v>46315.96991945978</v>
-      </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T46"/>
+  <autoFilter ref="A1:T45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
@@ -464,7 +464,7 @@
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="R2" s="5" t="n">
-        <v>46316.51961715194</v>
+        <v>46316.96723728769</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES GENVAL</t>
+          <t>FIP PROMISES BURRIANA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Genval</t>
+          <t>Burriana</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-valencia-2026-2/</t>
         </is>
       </c>
       <c r="K3" s="3" t="n">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="R3" s="5" t="n">
-        <v>46316.51962572482</v>
+        <v>46316.96724595972</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES BURRIANA</t>
+          <t>FIP PROMISES GENVAL</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Burriana</t>
+          <t>Genval</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-valencia-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="R4" s="5" t="n">
-        <v>46316.51963438129</v>
+        <v>46316.96725463247</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="R5" s="5" t="n">
-        <v>46316.51964310198</v>
+        <v>46316.96726313258</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="R6" s="5" t="n">
-        <v>46316.51965178905</v>
+        <v>46316.9672716643</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="R7" s="5" t="n">
-        <v>46316.51966041044</v>
+        <v>46316.96728072461</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="R8" s="5" t="n">
-        <v>46316.51966875415</v>
+        <v>46316.96728947633</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="R9" s="5" t="n">
-        <v>46316.51967716745</v>
+        <v>46316.9672980861</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="R10" s="5" t="n">
-        <v>46316.51968584171</v>
+        <v>46316.96730683328</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="R11" s="5" t="n">
-        <v>46316.51969449667</v>
+        <v>46316.96731539398</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES VILNIUS</t>
+          <t>FIP PROMISES TÖNISVORST</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Tönisvorst</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -1353,14 +1353,10 @@
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-vilnius/</t>
+          <t>https://www.padelfip.com/events/fip-promises-tonisvorst/</t>
         </is>
       </c>
       <c r="K12" s="3" t="n">
@@ -1383,7 +1379,7 @@
         </is>
       </c>
       <c r="R12" s="5" t="n">
-        <v>46316.51970290064</v>
+        <v>46316.96732395924</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
@@ -1399,7 +1395,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES TÖNISVORST</t>
+          <t>FIP PROMISES EL PRAT DE LLOBREGAT II</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1409,12 +1405,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Tönisvorst</t>
+          <t>El Prat de Llobregat</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -1429,10 +1425,14 @@
         </is>
       </c>
       <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-tonisvorst/</t>
+          <t>https://www.padelfip.com/events/fip-promises-el-prat-de-llobregat-ii-2026/</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="R13" s="5" t="n">
-        <v>46316.51971145446</v>
+        <v>46316.96733267589</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES EL PRAT DE LLOBREGAT II</t>
+          <t>FIP PROMISES MOUNTAIN VIEW</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>El Prat de Llobregat</t>
+          <t>Mountain View</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Cairo Egypt</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -1501,14 +1501,10 @@
         </is>
       </c>
       <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-el-prat-de-llobregat-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-mountain-view/</t>
         </is>
       </c>
       <c r="K14" s="3" t="n">
@@ -1531,7 +1527,7 @@
         </is>
       </c>
       <c r="R14" s="5" t="n">
-        <v>46316.51972025977</v>
+        <v>46316.96734134549</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1543,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES MOUNTAIN VIEW</t>
+          <t>FIP PROMISES VILNIUS</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1557,12 +1553,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Mountain View</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Cairo Egypt</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -1577,10 +1573,14 @@
         </is>
       </c>
       <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-mountain-view/</t>
+          <t>https://www.padelfip.com/events/fip-promises-vilnius/</t>
         </is>
       </c>
       <c r="K15" s="3" t="n">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="R15" s="5" t="n">
-        <v>46316.51972876854</v>
+        <v>46316.96735000441</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="R16" s="5" t="n">
-        <v>46316.51973746283</v>
+        <v>46316.96735864602</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="R17" s="5" t="n">
-        <v>46316.5197459172</v>
+        <v>46316.96736799814</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>46316.51975451063</v>
+        <v>46316.96737913343</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE LEVANTE</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nola</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-levante-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="R19" s="5" t="n">
-        <v>46316.51976307976</v>
+        <v>46316.96738782604</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MEDIOLANUM COMO</t>
+          <t>FIP BRONZE LEVANTE</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Nola</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-levante-2026/</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="R20" s="5" t="n">
-        <v>46316.51977187976</v>
+        <v>46316.96739675679</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2005,18 +2005,18 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
       <c r="K21" s="3" t="n">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="R21" s="5" t="n">
-        <v>46316.51978104881</v>
+        <v>46316.96740551048</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOHA II</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2081,18 +2081,18 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="R22" s="5" t="n">
-        <v>46316.51978954738</v>
+        <v>46316.96741429393</v>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="R23" s="5" t="n">
-        <v>46316.51979796115</v>
+        <v>46316.96742506641</v>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MCV PADELNESS</t>
+          <t>FIP SILVER GO PARK HONG KONG</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
@@ -2255,12 +2255,12 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>Fee €40 per player</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="R24" s="5" t="n">
-        <v>46316.51980648647</v>
+        <v>46316.96743378416</v>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE SWEDEN II</t>
+          <t>FIP SILVER MCV PADELNESS</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
@@ -2336,14 +2336,14 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>46332</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="R25" s="5" t="n">
-        <v>46316.51981506729</v>
+        <v>46316.96744241674</v>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CHILE IX</t>
+          <t>FIP BRONZE SWEDEN II</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2385,18 +2385,18 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Skurup</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2407,22 +2407,26 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="4" t="n"/>
+        <v>46347</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O26" s="3" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="2" t="inlineStr">
@@ -2431,15 +2435,23 @@
         </is>
       </c>
       <c r="R26" s="5" t="n">
-        <v>46316.51982378155</v>
-      </c>
-      <c r="S26" s="2" t="n"/>
-      <c r="T26" s="2" t="n"/>
+        <v>46316.96745230047</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE KARACHI II</t>
+          <t>FIP BRONZE CHILE IX</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2449,18 +2461,18 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2471,12 +2483,12 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
@@ -2485,12 +2497,8 @@
       <c r="L27" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="M27" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="4" t="n"/>
       <c r="O27" s="3" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="2" t="inlineStr">
@@ -2499,23 +2507,15 @@
         </is>
       </c>
       <c r="R27" s="5" t="n">
-        <v>46316.51983223663</v>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>página FIP</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Paris</t>
-        </is>
-      </c>
+        <v>46316.96746091418</v>
+      </c>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROCHEFORT</t>
+          <t>FIP BRONZE KARACHI II</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2525,18 +2525,18 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Rochefort</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
       <c r="K28" s="3" t="n">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="R28" s="5" t="n">
-        <v>46316.51984064467</v>
+        <v>46316.96746980036</v>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE IURRETA PADELKO</t>
+          <t>FIP BRONZE ROCHEFORT</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2601,18 +2601,18 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Iurreta</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="R29" s="5" t="n">
-        <v>46316.51984940693</v>
+        <v>46316.96747861279</v>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ACCRA – GHANA</t>
+          <t>FIP BRONZE IURRETA PADELKO</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Iurreta</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
@@ -2699,12 +2699,12 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="R30" s="5" t="n">
-        <v>46316.51985796809</v>
+        <v>46316.96748733678</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER GO PARK HONG KONG</t>
+          <t>FIP BRONZE ACCRA – GHANA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
@@ -2775,12 +2775,12 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Fee €40 per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="R31" s="5" t="n">
-        <v>46316.51986672306</v>
+        <v>46316.96749598366</v>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="R32" s="5" t="n">
-        <v>46316.51987525797</v>
+        <v>46316.9675044331</v>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="R33" s="5" t="n">
-        <v>46316.51988432642</v>
+        <v>46316.96751351842</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="R34" s="5" t="n">
-        <v>46316.51989256039</v>
+        <v>46316.96752209869</v>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="R35" s="5" t="n">
-        <v>46316.51990121895</v>
+        <v>46316.96753053322</v>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
@@ -3177,11 +3177,11 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Torneio a decorrer</t>
         </is>
       </c>
       <c r="R36" s="5" t="n">
-        <v>46316.51991461811</v>
+        <v>46316.96754423219</v>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="R37" s="5" t="n">
-        <v>46316.51991463084</v>
+        <v>46316.96754424616</v>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
+          <t>Carvoeiro Cup Veteranos</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Carvoeiro</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3303,21 +3303,21 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>GRIP - Grande Indoor Padel</t>
+          <t>Carvoeiro Clube de Ténis</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>VET M&amp;F +35 a +60</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>MASTERS</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -3326,50 +3326,34 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://fpp.tiepadel.com/tournaments/CarvoeiroCupVets26</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>46322</v>
+        <v>46317</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>46317</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46320</v>
+      </c>
+      <c r="M38" s="3" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="3" t="n"/>
+      <c r="P38" s="4" t="n"/>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições ainda não abriram</t>
         </is>
       </c>
       <c r="R38" s="5" t="n">
-        <v>46316.51991465061</v>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+        <v>46316.96754425717</v>
+      </c>
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
+          <t>Open Lemonfit Olaias</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3379,7 +3363,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3389,21 +3373,21 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ultra Padel Club</t>
+          <t>Lemonfit Olaias</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>M&amp;F: S12, S14, S16, S18</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -3412,50 +3396,34 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenJovLemonfit26</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46320</v>
+      </c>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="4" t="n"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições ainda não abriram</t>
         </is>
       </c>
       <c r="R39" s="5" t="n">
-        <v>46316.51991466397</v>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+        <v>46316.96754426797</v>
+      </c>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Open Luximos Christie's 2026</t>
+          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3465,7 +3433,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Pinhal Novo</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3475,7 +3443,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Your Top-padel Industrial</t>
+          <t>GRIP - Grande Indoor Padel</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3498,11 +3466,11 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>46327</v>
@@ -3517,7 +3485,7 @@
         <v>46317</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
@@ -3525,7 +3493,7 @@
         </is>
       </c>
       <c r="R40" s="5" t="n">
-        <v>46316.51991468055</v>
+        <v>46316.96754428194</v>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
@@ -3541,7 +3509,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3551,7 +3519,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3561,7 +3529,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>W Padel Ténis &amp; Parque</t>
+          <t>Ultra Padel Club</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3584,17 +3552,17 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>46327</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.625</v>
@@ -3607,11 +3575,11 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Pagamentos a decorrer</t>
         </is>
       </c>
       <c r="R41" s="5" t="n">
-        <v>46316.51991469382</v>
+        <v>46316.96754429588</v>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
@@ -3627,7 +3595,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+          <t>IX Open PSC Veteranos</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3637,7 +3605,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3647,21 +3615,21 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Dezporvinte</t>
+          <t>Padel Sports Club</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>VET M&amp;F +35 a +60</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>MASTERS</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3670,50 +3638,34 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+          <t>https://fpp.tiepadel.com/tournaments/IXOpenVetPSCbyAguasCaramulo26</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>46332</v>
+        <v>46323</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>46327</v>
+      </c>
+      <c r="M42" s="3" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="3" t="n"/>
+      <c r="P42" s="4" t="n"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições ainda não abriram</t>
         </is>
       </c>
       <c r="R42" s="5" t="n">
-        <v>46316.51991471186</v>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>detalhe</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+        <v>46316.9675443067</v>
+      </c>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Open Caetano</t>
+          <t>Open Luximos Christie's 2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3723,7 +3675,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3733,7 +3685,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Monserrate Gaia</t>
+          <t>Your Top-padel Industrial</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3756,34 +3708,34 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>46322</v>
+        <v>46315</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>46324</v>
+        <v>46317</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Pagamentos a decorrer</t>
         </is>
       </c>
       <c r="R43" s="5" t="n">
-        <v>46316.51991472463</v>
+        <v>46316.96754432057</v>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
@@ -3799,7 +3751,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Open DL Cozinhas Míele</t>
+          <t>III Open W Padel &amp; Ténis Parque</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3809,7 +3761,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3819,7 +3771,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>PAC - Padel Athletic Club</t>
+          <t>W Padel Ténis &amp; Parque</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3833,7 +3785,7 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -3842,96 +3794,898 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>46335</v>
+        <v>46325</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>46341</v>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="4" t="n"/>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="4" t="n"/>
+        <v>46327</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Pagamentos a decorrer</t>
         </is>
       </c>
       <c r="R44" s="5" t="n">
-        <v>46316.5199147454</v>
-      </c>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="2" t="n"/>
+        <v>46316.96754433406</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Dezporvinte</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>46316.96754435449</v>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Open Caetano</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Quinta de Monserrate Gaia</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>46316.96754436852</v>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>detalhe</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Gentlemen's &amp; Ladies Crew by OPA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Oeiras</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Oeiras Padel Academy</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>VET M&amp;F +35 a +60</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/TheGentlemenLadiesCrewOPA</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>46316.96754437975</v>
+      </c>
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Ii Open Jovem Carcavelos Ténis e Padel</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Carcavelos</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Carcavelos Ténis e Padel</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;F: S12, S14, S16, S18</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/ii-open-jovem-carcavelos-tenis-e-padel-jov-2026-11-06</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>46316.96754439006</v>
+      </c>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Open DL Cozinhas Míele</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>PAC - Padel Athletic Club</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M49" s="3" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="3" t="n"/>
+      <c r="P49" s="4" t="n"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>46316.96754440396</v>
+      </c>
+      <c r="S49" s="2" t="n"/>
+      <c r="T49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>I Torneio SPM</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Mafra</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sport Padel Mafra</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/i-torneio-spm-abs-2026-11-12</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M50" s="3" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>46316.96754441427</v>
+      </c>
+      <c r="S50" s="2" t="n"/>
+      <c r="T50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>FINAL LIGA de CLUBES VETERANOS</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Caldas da Rainha</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>M &amp; F</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/78f940e5-cf76-475a-9a6d-76aaf9daf59a</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>46316.96754443042</v>
+      </c>
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>1º Open Jovem W Padel &amp; Ténis Parque</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Barreiro</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>W Padel Ténis &amp; Parque</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;F: S12, S14, S16, S18</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/1openJOVWPadel26</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M52" s="3" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>46316.96754444129</v>
+      </c>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>FPP Portugal</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>FPP</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>M &amp; F</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K53" s="3" t="n">
         <v>46345</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L53" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="4" t="n"/>
-      <c r="O45" s="3" t="n"/>
-      <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="3" t="n"/>
+      <c r="P53" s="4" t="n"/>
+      <c r="Q53" s="2" t="inlineStr">
         <is>
           <t>Inscrições fechadas</t>
         </is>
       </c>
-      <c r="R45" s="5" t="n">
-        <v>46316.51991477024</v>
-      </c>
-      <c r="S45" s="2" t="n"/>
-      <c r="T45" s="2" t="n"/>
+      <c r="R53" s="5" t="n">
+        <v>46316.96754445804</v>
+      </c>
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Masters Final FPP Jovens</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Algarve</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/masters-final-fpp-jovens-jov-2026-11-27</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>46353</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M54" s="3" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="4" t="n"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>46316.96754447508</v>
+      </c>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Masters Final FPP Veteranos</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Algarve</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/masters-final-fpp-veteranos-vet-2026-11-27</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>46353</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="3" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>46316.96754449209</v>
+      </c>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Masters Final FPP Absoluto</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Paredes</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/masters-final-fpp-absoluto-abs-2026-11-27</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>46353</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M56" s="3" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>46316.96754450921</v>
+      </c>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T45"/>
+  <autoFilter ref="A1:T56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,13 +445,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -575,17 +575,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Open A-Z Padel Guimarães</t>
+          <t>FIP PROMISES LISBOA RACKET CENTRE</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -593,272 +593,238 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Top-padel Guimarães</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+          <t>https://www.padelfip.com/events/fip-promises-lisboa-racket-centre-2026/</t>
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>46316</v>
+        <v>46331</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>46320</v>
+        <v>46334</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>46310</v>
+        <v>46323</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>46312</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="4" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Torneio a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R2" s="5" t="n">
-        <v>46317.48309059506</v>
+        <v>46317.50644337769</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>5º Open Padcenter</t>
+          <t>FIP PROMISES GENVAL</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Odivelas</t>
+          <t>Genval</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Padcenter Odivelas</t>
-        </is>
-      </c>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+          <t>https://www.padelfip.com/events/fip-promises-waver-2026/</t>
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>46317</v>
+        <v>46338</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>46320</v>
+        <v>46341</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>46309</v>
+        <v>46323</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="4" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R3" s="5" t="n">
-        <v>46317.48309060858</v>
+        <v>46317.50645176368</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Cup Veteranos</t>
+          <t>FIP PROMISES BURRIANA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro</t>
+          <t>Burriana</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Carvoeiro Clube de Ténis</t>
-        </is>
-      </c>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>VET M&amp;F +35 a +60</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/CarvoeiroCupVets26</t>
+          <t>https://www.padelfip.com/events/fip-promises-valencia-2026-2/</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>46317</v>
+        <v>46338</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>46320</v>
+        <v>46341</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>46310</v>
+        <v>46323</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="4" t="n"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R4" s="5" t="n">
-        <v>46317.48309061927</v>
+        <v>46317.5064602992</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Open Lemonfit Olaias</t>
+          <t>FIP PROMISES KETAMEYA HEIGHTS</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Lemonfit Olaias</t>
-        </is>
-      </c>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>M&amp;F: S12, S14, S16, S18</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,632 +832,544 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenJovLemonfit26</t>
+          <t>https://www.padelfip.com/events/fip-promises-ketameya-heights-2026/</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>46318</v>
+        <v>46339</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>46320</v>
+        <v>46341</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>46309</v>
+        <v>46323</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>46311</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.375</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="4" t="n"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Inscrições fechadas</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R5" s="5" t="n">
-        <v>46317.4830906303</v>
+        <v>46317.50646861244</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
+          <t>FIP PROMISES DOHA II</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>GRIP - Grande Indoor Padel</t>
-        </is>
-      </c>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>5000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://www.padelfip.com/events/fip-promises-doha-iii/</t>
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>46322</v>
+        <v>46344</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46327</v>
+        <v>46348</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="4" t="n"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R6" s="5" t="n">
-        <v>46317.48309064425</v>
+        <v>46317.50647701868</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
+          <t>FIP PROMISES ROESELARE</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Ultra Padel Club</t>
-        </is>
-      </c>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>46323</v>
+        <v>46345</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>46327</v>
+        <v>46348</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>46317</v>
+        <v>46330</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="4" t="n"/>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R7" s="5" t="n">
-        <v>46317.48309065789</v>
+        <v>46317.50648571737</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>IX Open PSC Veteranos</t>
+          <t>FIP PROMISES PERUGIA III</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Padel Sports Club</t>
-        </is>
-      </c>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>VET M&amp;F +35 a +60</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IXOpenVetPSCbyAguasCaramulo26</t>
+          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>46323</v>
+        <v>46345</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>46327</v>
+        <v>46348</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>46317</v>
+        <v>46330</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>46319</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="4" t="n"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R8" s="5" t="n">
-        <v>46317.48309066885</v>
+        <v>46317.50649405639</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Open Luximos Christie's 2026</t>
+          <t>FIP PROMISES HONG KONG V</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Your Top-padel Industrial</t>
-        </is>
-      </c>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+          <t>https://www.padelfip.com/events/fip-promises-hong-kong-v/</t>
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>46325</v>
+        <v>46346</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>46327</v>
+        <v>46348</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>46316</v>
+        <v>46330</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="4" t="n"/>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R9" s="5" t="n">
-        <v>46317.48309068274</v>
+        <v>46317.50650245316</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
+          <t>FIP PROMISES LLEIDA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W Padel Ténis &amp; Parque</t>
-        </is>
-      </c>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>46325</v>
+        <v>46352</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>46327</v>
+        <v>46355</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>46316</v>
+        <v>46337</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="4" t="n"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R10" s="5" t="n">
-        <v>46317.48309069616</v>
+        <v>46317.50651089859</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+          <t>FIP PROMISES RENDE</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Rende</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Dezporvinte</t>
-        </is>
-      </c>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>46332</v>
+        <v>46352</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>46334</v>
+        <v>46355</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>46322</v>
+        <v>46337</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R11" s="5" t="n">
-        <v>46317.48309071644</v>
+        <v>46317.50651871175</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Open Caetano</t>
+          <t>FIP PROMISES MOUNTAIN VIEW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Mountain View</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Quinta de Monserrate Gaia</t>
-        </is>
-      </c>
+          <t>Cairo Egypt</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+          <t>https://www.padelfip.com/events/fip-promises-mountain-view/</t>
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>46332</v>
+        <v>46359</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>46334</v>
+        <v>46362</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>46322</v>
+        <v>46344</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="O12" s="3" t="n"/>
       <c r="P12" s="4" t="n"/>
@@ -1501,79 +1379,73 @@
         </is>
       </c>
       <c r="R12" s="5" t="n">
-        <v>46317.48309073027</v>
+        <v>46317.50652717856</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>site (dado suspeito)</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Gentlemen's &amp; Ladies Crew by OPA</t>
+          <t>FIP PROMISES VILNIUS</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Oeiras Padel Academy</t>
-        </is>
-      </c>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>VET M&amp;F +35 a +60</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/TheGentlemenLadiesCrewOPA</t>
+          <t>https://www.padelfip.com/events/fip-promises-vilnius/</t>
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>46332</v>
+        <v>46359</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>46334</v>
+        <v>46362</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>46322</v>
+        <v>46344</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="O13" s="3" t="n"/>
       <c r="P13" s="4" t="n"/>
@@ -1583,48 +1455,44 @@
         </is>
       </c>
       <c r="R13" s="5" t="n">
-        <v>46317.48309074177</v>
+        <v>46317.50653558816</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>site (dado suspeito)</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Ii Open Jovem Carcavelos Ténis e Padel</t>
+          <t>FIP PROMISES TÖNISVORST</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Carcavelos</t>
+          <t>Tönisvorst</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Carcavelos Ténis e Padel</t>
-        </is>
-      </c>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>M&amp;F: S12, S14, S16, S18</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1632,159 +1500,147 @@
           <t>JUNIOR</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>/torneios/ii-open-jovem-carcavelos-tenis-e-padel-jov-2026-11-06</t>
+          <t>https://www.padelfip.com/events/fip-promises-tonisvorst/</t>
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46332</v>
+        <v>46359</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="4" t="n"/>
+        <v>46362</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>46344</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="O14" s="3" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Inscrições ainda não abriram</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R14" s="5" t="n">
-        <v>46317.48309075135</v>
+        <v>46317.50654405371</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="n"/>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Open DL Cozinhas Míele</t>
+          <t>FIP PROMISES EL PRAT DE LLOBREGAT II</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>Promises</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>El Prat de Llobregat</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>PAC - Padel Athletic Club</t>
-        </is>
-      </c>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>10000</v>
-      </c>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>25€ per player/category</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
+          <t>https://www.padelfip.com/events/fip-promises-el-prat-de-llobregat-ii-2026/</t>
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>46335</v>
+        <v>46359</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>46341</v>
+        <v>46362</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>46329</v>
+        <v>46344</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="4" t="n"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R15" s="5" t="n">
-        <v>46317.48309076426</v>
+        <v>46317.50655248602</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>I Torneio SPM</t>
+          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Mafra</t>
+          <t>Malé</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Sport Padel Mafra</t>
-        </is>
-      </c>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1792,231 +1648,223 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>/torneios/i-torneio-spm-abs-2026-11-12</t>
+          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46338</v>
+        <v>46328</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46341</v>
-      </c>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="4" t="n"/>
+        <v>46334</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O16" s="3" t="n"/>
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Inscrições ainda não abriram</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R16" s="5" t="n">
-        <v>46317.48309077448</v>
+        <v>46317.50656099025</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="n"/>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FINAL LIGA de CLUBES VETERANOS</t>
+          <t>FIP BRONZE CYPRUS IV</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Caldas da Rainha</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
+          <t>Ayia Napa / Cyprus</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>M &amp; F</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40€ per player</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/78f940e5-cf76-475a-9a6d-76aaf9daf59a</t>
+          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46338</v>
+        <v>46328</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46341</v>
-      </c>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="4" t="n"/>
+        <v>46334</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O17" s="3" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Inscrições ainda não abriram</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R17" s="5" t="n">
-        <v>46317.4830907904</v>
+        <v>46317.50656947007</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="n"/>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1º Open Jovem W Padel &amp; Ténis Parque</t>
+          <t>FIP BRONZE ESC PADEL</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Espoo</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>W Padel Ténis &amp; Parque</t>
-        </is>
-      </c>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>M&amp;F: S12, S14, S16, S18</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>5000</v>
-      </c>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openJOVWPadel26</t>
+          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46339</v>
+        <v>46328</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>46341</v>
+        <v>46334</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>46330</v>
+        <v>46318</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>0.375</v>
-      </c>
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="4" t="n"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>46317.48309080138</v>
+        <v>46317.50657810839</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>página FIP</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>Europe/Lisbon</t>
+          <t>Europe/Paris</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
+          <t>FIP BRONZE LEVANTE</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Nola</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>M &amp; F</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2027,202 +1875,226 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
+          <t>https://www.padelfip.com/events/fip-bronze-levante-2026/</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>46345</v>
+        <v>46335</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="4" t="n"/>
+        <v>46341</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O19" s="3" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Inscrições ainda não abriram</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R19" s="5" t="n">
-        <v>46317.48309081779</v>
+        <v>46317.50658650012</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="n"/>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Masters Final FPP Jovens</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Algarve</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n"/>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>/torneios/masters-final-fpp-jovens-jov-2026-11-27</t>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>46353</v>
+        <v>46335</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46355</v>
-      </c>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="4" t="n"/>
+        <v>46341</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Inscrições ainda não abriram</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R20" s="5" t="n">
-        <v>46317.48309083466</v>
+        <v>46317.50659516613</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="n"/>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Masters Final FPP Veteranos</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Algarve</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n"/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>/torneios/masters-final-fpp-veteranos-vet-2026-11-27</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>46353</v>
+        <v>46335</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46355</v>
-      </c>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="4" t="n"/>
+        <v>46341</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O21" s="3" t="n"/>
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Inscrições ainda não abriram</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R21" s="5" t="n">
-        <v>46317.48309085143</v>
+        <v>46317.5066035557</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="n"/>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Masters Final FPP Absoluto</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FPP Portugal</t>
+          <t>CUPRA Tour</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n"/>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>MAIN</t>
@@ -2231,41 +2103,2709 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Ver regulamento interno</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>/torneios/masters-final-fpp-absoluto-abs-2026-11-27</t>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46353</v>
+        <v>46335</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46355</v>
-      </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="4" t="n"/>
+        <v>46341</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>46317.50661231345</v>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>FIP PLATINUM AGUASCALIENTES</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>40 € per player</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>46347</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>46317.50662078749</v>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE SWEDEN II</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Skurup</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>40 € per player</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>46347</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>46317.50662871789</v>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE CHILE IX</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>30 € per player</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>46317.50663637677</v>
+      </c>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE KARACHI II</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Karachi</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>40€</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>46317.50664481183</v>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE ROCHEFORT</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Rochefort</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>40 Euros per player</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>46317.50665313269</v>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE IURRETA PADELKO</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Iurreta</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>40 € per player</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>46317.50666156533</v>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE ACCRA – GHANA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Accra</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>40€</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>46317.5066700445</v>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FIP SILVER GO PARK HONG KONG</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Fee €40 per player</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>46317.50667850648</v>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>FIP SILVER MCV PADELNESS</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>40 € per player</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>46317.50668671368</v>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FIP SILVER ROESELARE</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Roeselare</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>46317.50669519206</v>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE DOVY PADEL OPEN</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Roeselare</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>30 € per player</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-dovy-padel-open-2026/</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>46317.50670357076</v>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE DENIA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Denia</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>40 € per player</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>46317.50671190135</v>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>CUPRA Tour</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Phuket</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Female/Male</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="4" t="n"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>46317.50672022226</v>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Open A-Z Padel Guimarães</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Guimarães</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Top-padel Guimarães</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Torneio a decorrer</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>46317.5067306403</v>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>5º Open Padcenter</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Odivelas</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Padcenter Odivelas</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições fechadas</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>46317.50673065319</v>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Carvoeiro Cup Veteranos</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Carvoeiro</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Carvoeiro Clube de Ténis</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>VET M&amp;F +35 a +60</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/CarvoeiroCupVets26</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições fechadas</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="n">
+        <v>46317.5067306634</v>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Open Lemonfit Olaias</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Lemonfit Olaias</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;F: S12, S14, S16, S18</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenJovLemonfit26</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições fechadas</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>46317.50673067357</v>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Pinhal Novo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>GRIP - Grande Indoor Padel</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Pagamentos a decorrer</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>46317.506730687</v>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Ultra Padel Club</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>46317.50673070055</v>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>IX Open PSC Veteranos</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Sintra</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Padel Sports Club</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>VET M&amp;F +35 a +60</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/IXOpenVetPSCbyAguasCaramulo26</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="n">
+        <v>46317.50673071156</v>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Open Luximos Christie's 2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Your Top-padel Industrial</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>Pagamentos a decorrer</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>46317.50673072465</v>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>III Open W Padel &amp; Ténis Parque</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Barreiro</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>W Padel Ténis &amp; Parque</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>Pagamentos a decorrer</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>46317.50673073744</v>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Dezporvinte</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="n">
+        <v>46317.50673075693</v>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Open Caetano</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Quinta de Monserrate Gaia</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="4" t="n"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>46317.50673077094</v>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>site (dado suspeito)</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Gentlemen's &amp; Ladies Crew by OPA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Oeiras</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Oeiras Padel Academy</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>VET M&amp;F +35 a +60</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/TheGentlemenLadiesCrewOPA</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O47" s="3" t="n"/>
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>46317.50673078245</v>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>site (dado suspeito)</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Ii Open Jovem Carcavelos Ténis e Padel</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Carcavelos</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Carcavelos Ténis e Padel</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;F: S12, S14, S16, S18</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/ii-open-jovem-carcavelos-tenis-e-padel-jov-2026-11-06</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>46334</v>
+      </c>
+      <c r="M48" s="3" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="3" t="n"/>
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
           <t>Inscrições ainda não abriram</t>
         </is>
       </c>
-      <c r="R22" s="5" t="n">
-        <v>46317.48309086824</v>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="R48" s="5" t="n">
+        <v>46317.50673079224</v>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="T22" s="2" t="n"/>
+      <c r="T48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Open DL Cozinhas Míele</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>PAC - Padel Athletic Club</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>46329</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>46317.50673080547</v>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>I Torneio SPM</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Mafra</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sport Padel Mafra</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>F1-F6; M1-M6</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/i-torneio-spm-abs-2026-11-12</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M50" s="3" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="4" t="n"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>46317.50673081545</v>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>FINAL LIGA de CLUBES VETERANOS</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Caldas da Rainha</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>M &amp; F</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/78f940e5-cf76-475a-9a6d-76aaf9daf59a</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M51" s="3" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="3" t="n"/>
+      <c r="P51" s="4" t="n"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>46317.50673083162</v>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>1º Open Jovem W Padel &amp; Ténis Parque</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Barreiro</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>W Padel Ténis &amp; Parque</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;F: S12, S14, S16, S18</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/1openJOVWPadel26</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>46339</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>46341</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>46330</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições abertas</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>46317.50673084318</v>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Lisbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>M &amp; F</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>46345</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M53" s="3" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="3" t="n"/>
+      <c r="P53" s="4" t="n"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>46317.50673085986</v>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Masters Final FPP Jovens</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Algarve</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>JUNIOR</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/masters-final-fpp-jovens-jov-2026-11-27</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>46353</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M54" s="3" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="4" t="n"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>46317.50673087596</v>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Masters Final FPP Veteranos</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Algarve</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/masters-final-fpp-veteranos-vet-2026-11-27</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>46353</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="3" t="n"/>
+      <c r="P55" s="4" t="n"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>46317.50673089265</v>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Masters Final FPP Absoluto</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>FPP Portugal</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Paredes</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>/torneios/masters-final-fpp-absoluto-abs-2026-11-27</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>46353</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>46355</v>
+      </c>
+      <c r="M56" s="3" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Inscrições ainda não abriram</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>46317.50673090955</v>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T22"/>
+  <autoFilter ref="A1:T56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TorneiosPadel_InscricoesAbertas.xlsx
+++ b/TorneiosPadel_InscricoesAbertas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Torneios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Torneios'!$A$1:$T$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="R2" s="5" t="n">
-        <v>46317.50644337769</v>
+        <v>46320.39181057396</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="R3" s="5" t="n">
-        <v>46317.50645176368</v>
+        <v>46320.39181881437</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="R4" s="5" t="n">
-        <v>46317.5064602992</v>
+        <v>46320.39182713303</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="R5" s="5" t="n">
-        <v>46317.50646861244</v>
+        <v>46320.39183551471</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="R6" s="5" t="n">
-        <v>46317.50647701868</v>
+        <v>46320.39184407306</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES ROESELARE</t>
+          <t>FIP PROMISES PERUGIA III</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="R7" s="5" t="n">
-        <v>46317.50648571737</v>
+        <v>46320.39185258799</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES PERUGIA III</t>
+          <t>FIP PROMISES ROESELARE</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-perugia-iii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-roeselare-2026/</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="R8" s="5" t="n">
-        <v>46317.50649405639</v>
+        <v>46320.39186091466</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="R9" s="5" t="n">
-        <v>46317.50650245316</v>
+        <v>46320.3918691068</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES LLEIDA</t>
+          <t>FIP PROMISES RENDE</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Rende</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
@@ -1205,14 +1205,10 @@
         </is>
       </c>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25€ per player/category</t>
-        </is>
-      </c>
+      <c r="I10" s="2" t="n"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
@@ -1235,7 +1231,7 @@
         </is>
       </c>
       <c r="R10" s="5" t="n">
-        <v>46317.50651089859</v>
+        <v>46320.39187726333</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
@@ -1251,7 +1247,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>FIP PROMISES RENDE</t>
+          <t>FIP PROMISES LLEIDA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1261,12 +1257,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Rende</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -1281,10 +1277,14 @@
         </is>
       </c>
       <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25€ per player/category</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-promises-rende-2026/</t>
+          <t>https://www.padelfip.com/events/fip-promises-lleida-2026/</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="R11" s="5" t="n">
-        <v>46317.50651871175</v>
+        <v>46320.39188556098</v>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="R12" s="5" t="n">
-        <v>46317.50652717856</v>
+        <v>46320.39189415202</v>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="R13" s="5" t="n">
-        <v>46317.50653558816</v>
+        <v>46320.39190254124</v>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="R14" s="5" t="n">
-        <v>46317.50654405371</v>
+        <v>46320.39191082186</v>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="R15" s="5" t="n">
-        <v>46317.50655248602</v>
+        <v>46320.39191912537</v>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER WOMEN’S PADEL CROSSROADS MALDIVES</t>
+          <t>FIP SILVER MEDIOLANUM COMO</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1629,18 +1629,18 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Malé</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-womens-padel-crossroads-maldives-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="R16" s="5" t="n">
-        <v>46317.50656099025</v>
+        <v>46320.39192744778</v>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CYPRUS IV</t>
+          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1705,14 +1705,18 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ayia Napa / Cyprus</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n"/>
+          <t>Kochi</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1723,22 +1727,22 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40€ per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-cyprus-iv-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1751,7 +1755,7 @@
         </is>
       </c>
       <c r="R17" s="5" t="n">
-        <v>46317.50656947007</v>
+        <v>46320.39193575013</v>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
@@ -1767,7 +1771,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ESC PADEL</t>
+          <t>FIP BRONZE DOHA II</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1777,12 +1781,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Espoo</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
@@ -1804,17 +1808,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-esc-padel-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>46328</v>
+        <v>46335</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1827,7 +1831,7 @@
         </is>
       </c>
       <c r="R18" s="5" t="n">
-        <v>46317.50657810839</v>
+        <v>46320.39194404666</v>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1907,7 @@
         </is>
       </c>
       <c r="R19" s="5" t="n">
-        <v>46317.50658650012</v>
+        <v>46320.39195243946</v>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
@@ -1919,7 +1923,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MEDIOLANUM COMO</t>
+          <t>FIP PLATINUM AGUASCALIENTES</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1929,12 +1933,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -1956,17 +1960,17 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mediolanum-como-2026/</t>
+          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>46335</v>
+        <v>46341</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46341</v>
+        <v>46347</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -1979,7 +1983,7 @@
         </is>
       </c>
       <c r="R20" s="5" t="n">
-        <v>46317.50659516613</v>
+        <v>46320.39196080266</v>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
@@ -1995,7 +1999,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY KOCHI</t>
+          <t>FIP BRONZE ROCHEFORT</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2005,12 +2009,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Rochefort</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -2027,22 +2031,22 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40 Euros per player</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-kochi-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2055,7 +2059,7 @@
         </is>
       </c>
       <c r="R21" s="5" t="n">
-        <v>46317.5066035557</v>
+        <v>46320.39196943875</v>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
@@ -2071,7 +2075,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOHA II</t>
+          <t>FIP BRONZE PADELKO</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2081,12 +2085,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Iurreta</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -2108,17 +2112,17 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-doha-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-padelko-2026/</t>
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>46335</v>
+        <v>46342</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2131,7 +2135,7 @@
         </is>
       </c>
       <c r="R22" s="5" t="n">
-        <v>46317.50661231345</v>
+        <v>46320.39197782486</v>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
@@ -2147,7 +2151,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>FIP PLATINUM AGUASCALIENTES</t>
+          <t>FIP BRONZE ACCRA – GHANA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2157,12 +2161,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Aguascalientes</t>
+          <t>Accra</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -2179,19 +2183,19 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-platinum-aguascalientes-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>46332</v>
@@ -2207,7 +2211,7 @@
         </is>
       </c>
       <c r="R23" s="5" t="n">
-        <v>46317.50662078749</v>
+        <v>46320.39198668785</v>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
@@ -2223,7 +2227,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE SWEDEN II</t>
+          <t>FIP SILVER GO PARK HONG KONG</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2233,12 +2237,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Skurup</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
@@ -2255,19 +2259,19 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>Fee €40 per player</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>46332</v>
@@ -2283,7 +2287,7 @@
         </is>
       </c>
       <c r="R24" s="5" t="n">
-        <v>46317.50662871789</v>
+        <v>46320.39199569625</v>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2303,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE CHILE IX</t>
+          <t>FIP SILVER MCV PADELNESS</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2309,18 +2313,18 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2331,12 +2335,12 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
+          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
@@ -2345,8 +2349,12 @@
       <c r="L25" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="4" t="n"/>
+      <c r="M25" s="3" t="n">
+        <v>46332</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="O25" s="3" t="n"/>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="2" t="inlineStr">
@@ -2355,15 +2363,23 @@
         </is>
       </c>
       <c r="R25" s="5" t="n">
-        <v>46317.50663637677</v>
-      </c>
-      <c r="S25" s="2" t="n"/>
-      <c r="T25" s="2" t="n"/>
+        <v>46320.39200414463</v>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>página FIP</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Europe/Paris</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE KARACHI II</t>
+          <t>FIP BRONZE CHILE IX</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2373,18 +2389,18 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Karachi</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2395,12 +2411,12 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-chile-ix-2026-2/</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
@@ -2409,12 +2425,8 @@
       <c r="L26" s="3" t="n">
         <v>46348</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="4" t="n"/>
       <c r="O26" s="3" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="2" t="inlineStr">
@@ -2423,23 +2435,15 @@
         </is>
       </c>
       <c r="R26" s="5" t="n">
-        <v>46317.50664481183</v>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>página FIP</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Paris</t>
-        </is>
-      </c>
+        <v>46320.39201242055</v>
+      </c>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ROCHEFORT</t>
+          <t>FIP BRONZE SWEDEN II</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2449,18 +2453,18 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Rochefort</t>
+          <t>Skurup</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2471,19 +2475,19 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40 Euros per player</t>
+          <t>40 € per player</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-rochefort-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-sweden-ii-2026/</t>
         </is>
       </c>
       <c r="K27" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>46332</v>
@@ -2499,7 +2503,7 @@
         </is>
       </c>
       <c r="R27" s="5" t="n">
-        <v>46317.50665313269</v>
+        <v>46320.39202092635</v>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2519,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE IURRETA PADELKO</t>
+          <t>FIP BRONZE KARACHI II</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2525,12 +2529,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Iurreta</t>
+          <t>Karachi</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E28" s="2" t="n"/>
@@ -2547,12 +2551,12 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>40€</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-vizcaya-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-karachi-ii-2026/</t>
         </is>
       </c>
       <c r="K28" s="3" t="n">
@@ -2575,7 +2579,7 @@
         </is>
       </c>
       <c r="R28" s="5" t="n">
-        <v>46317.50666156533</v>
+        <v>46320.39202916915</v>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2595,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE ACCRA – GHANA</t>
+          <t>FIP SILVER DOVY PADEL OPEN</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2601,18 +2605,18 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Accra</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2623,22 +2627,22 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40€</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-accra-ghana-2026/</t>
+          <t>https://www.padelfip.com/events/fip-silver-dovy-padel-open-2026/</t>
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2651,7 +2655,7 @@
         </is>
       </c>
       <c r="R29" s="5" t="n">
-        <v>46317.5066700445</v>
+        <v>46320.39203768038</v>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
@@ -2667,7 +2671,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER GO PARK HONG KONG</t>
+          <t>FIP BRONZE DOVY PADEL OPEN</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2677,18 +2681,18 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Roeselare</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2699,22 +2703,22 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Fee €40 per player</t>
+          <t>30 € per player</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-hong-kong-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-dovy-padel-open-2026/</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2727,7 +2731,7 @@
         </is>
       </c>
       <c r="R30" s="5" t="n">
-        <v>46317.50667850648</v>
+        <v>46320.39204624382</v>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
@@ -2743,7 +2747,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER MCV PADELNESS</t>
+          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2753,12 +2757,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Phuket</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="E31" s="2" t="n"/>
@@ -2773,24 +2777,20 @@
         </is>
       </c>
       <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>40 € per player</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-mcv-padelness-2026/</t>
+          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>46342</v>
+        <v>46349</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="R31" s="5" t="n">
-        <v>46317.50668671368</v>
+        <v>46320.39205445482</v>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FIP SILVER ROESELARE</t>
+          <t>CUPRA FIP FINALS</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2829,18 +2829,18 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Tarragona</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female/Male</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2852,17 +2852,17 @@
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-silver-roeselare-2026/</t>
+          <t>https://www.padelfip.com/events/cupra-fip-finals/</t>
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>46349</v>
+        <v>46359</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46355</v>
+        <v>46362</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>46339</v>
+        <v>46353</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="R32" s="5" t="n">
-        <v>46317.50669519206</v>
+        <v>46320.39206261323</v>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
@@ -2891,28 +2891,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DOVY PADEL OPEN</t>
+          <t>Open A-Z Padel Guimarães</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Roeselare</t>
+          <t>Guimarães</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Top-padel Guimarães</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2920,75 +2924,85 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
+      <c r="H33" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>30 € per player</t>
+          <t>Ver regulamento interno</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-dovy-padel-open-2026/</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>46349</v>
+        <v>46316</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46355</v>
+        <v>46320</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>46339</v>
+        <v>46310</v>
       </c>
       <c r="N33" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="P33" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="4" t="n"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Torneio a decorrer</t>
         </is>
       </c>
       <c r="R33" s="5" t="n">
-        <v>46317.50670357076</v>
+        <v>46320.39207326927</v>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>site</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE DENIA</t>
+          <t>5º Open Padcenter</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Denia</t>
+          <t>Odivelas</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Padcenter Odivelas</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2996,126 +3010,146 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
+      <c r="H34" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40 € per player</t>
+          <t>Ver regulamento interno</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-denia-2026/</t>
+          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>46349</v>
+        <v>46317</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46355</v>
+        <v>46320</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>46339</v>
+        <v>46309</v>
       </c>
       <c r="N34" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="P34" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="4" t="n"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="R34" s="5" t="n">
-        <v>46317.50671190135</v>
+        <v>46320.39207328336</v>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>site</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FIP BRONZE HIGH VELOCITY PHUKET</t>
+          <t>Carvoeiro Cup Veteranos</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CUPRA Tour</t>
+          <t>FPP Portugal</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Phuket</t>
+          <t>Carvoeiro</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n"/>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Carvoeiro Clube de Ténis</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Female/Male</t>
+          <t>VET M&amp;F +35 a +60</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Ver regulamento interno</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>https://www.padelfip.com/events/fip-bronze-high-velocity-phuket-2026-2/</t>
+          <t>https://fpp.tiepadel.com/tournaments/CarvoeiroCupVets26</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>46349</v>
+        <v>46317</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46355</v>
+        <v>46320</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>46339</v>
+        <v>46310</v>
       </c>
       <c r="N35" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="P35" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="O35" s="3" t="n"/>
-      <c r="P35" s="4" t="n"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="R35" s="5" t="n">
-        <v>46317.50672022226</v>
+        <v>46320.39207329461</v>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>página FIP</t>
+          <t>site</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>Europe/Paris</t>
+          <t>Europe/Lisbon</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Open A-Z Padel Guimarães</t>
+          <t>Open Lemonfit Olaias</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -3125,7 +3159,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Guimarães</t>
+          <t>Lisboa</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3135,21 +3169,21 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Top-padel Guimarães</t>
+          <t>Lemonfit Olaias</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>M&amp;F: S12, S14, S16, S18</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -3158,34 +3192,34 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenAZPadelGuimaraes</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenJovLemonfit26</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>46320</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.375</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Torneio a decorrer</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="R36" s="5" t="n">
-        <v>46317.5067306403</v>
+        <v>46320.39207330576</v>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
@@ -3201,7 +3235,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>5º Open Padcenter</t>
+          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -3211,7 +3245,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Odivelas</t>
+          <t>Pinhal Novo</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3221,7 +3255,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Padcenter Odivelas</t>
+          <t>GRIP - Grande Indoor Padel</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3235,7 +3269,7 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -3244,23 +3278,23 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/5OpenPadCenter26</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3271,7 +3305,7 @@
         </is>
       </c>
       <c r="R37" s="5" t="n">
-        <v>46317.50673065319</v>
+        <v>46320.39207332009</v>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
@@ -3287,7 +3321,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Cup Veteranos</t>
+          <t>XI Open Ultra Padel Club by AJúlio</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3297,7 +3331,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro</t>
+          <t>Leiria</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3307,17 +3341,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Carvoeiro Clube de Ténis</t>
+          <t>Ultra Padel Club</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>VET M&amp;F +35 a +60</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
@@ -3330,23 +3364,23 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/CarvoeiroCupVets26</t>
+          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="M38" s="3" t="n">
         <v>46317</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>46320</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>46310</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3357,7 +3391,7 @@
         </is>
       </c>
       <c r="R38" s="5" t="n">
-        <v>46317.5067306634</v>
+        <v>46320.39207333393</v>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
@@ -3373,7 +3407,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Open Lemonfit Olaias</t>
+          <t>IX Open PSC Veteranos</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3383,7 +3417,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t>Sintra</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3393,21 +3427,21 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Lemonfit Olaias</t>
+          <t>Padel Sports Club</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>M&amp;F: S12, S14, S16, S18</t>
+          <t>VET M&amp;F +35 a +60</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
+          <t>MASTERS</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -3416,26 +3450,26 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenJovLemonfit26</t>
+          <t>https://fpp.tiepadel.com/tournaments/IXOpenVetPSCbyAguasCaramulo26</t>
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46318</v>
+        <v>46323</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>46309</v>
+        <v>46317</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.375</v>
+        <v>0.625</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>46311</v>
+        <v>46319</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>0.375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
@@ -3443,7 +3477,7 @@
         </is>
       </c>
       <c r="R39" s="5" t="n">
-        <v>46317.50673067357</v>
+        <v>46320.39207334506</v>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
@@ -3459,7 +3493,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1º Open de Absolutos GRIP by ESPAÇO PARA TUDO</t>
+          <t>Open Luximos Christie's 2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3469,7 +3503,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pinhal Novo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3479,7 +3513,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>GRIP - Grande Indoor Padel</t>
+          <t>Your Top-padel Industrial</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3502,11 +3536,11 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openDeAbsolutosByGRIP2026</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>46327</v>
@@ -3525,11 +3559,11 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="R40" s="5" t="n">
-        <v>46317.506730687</v>
+        <v>46320.39207335912</v>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
@@ -3545,7 +3579,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>XI Open Ultra Padel Club by AJúlio</t>
+          <t>III Open W Padel &amp; Ténis Parque</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3555,7 +3589,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Leiria</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3565,7 +3599,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Ultra Padel Club</t>
+          <t>W Padel Ténis &amp; Parque</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3588,34 +3622,34 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/XIOpenUltraPadelClubbyAJulio</t>
+          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>46327</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições fechadas</t>
         </is>
       </c>
       <c r="R41" s="5" t="n">
-        <v>46317.50673070055</v>
+        <v>46320.39207337286</v>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
@@ -3631,7 +3665,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>IX Open PSC Veteranos</t>
+          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3641,7 +3675,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Sintra</t>
+          <t>Santarém</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3651,21 +3685,21 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Padel Sports Club</t>
+          <t>Dezporvinte</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>VET M&amp;F +35 a +60</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3674,23 +3708,23 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IXOpenVetPSCbyAguasCaramulo26</t>
+          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>46323</v>
+        <v>46332</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>0.625</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>46319</v>
+        <v>46324</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0.7083333333333334</v>
@@ -3701,7 +3735,7 @@
         </is>
       </c>
       <c r="R42" s="5" t="n">
-        <v>46317.50673071156</v>
+        <v>46320.39207339368</v>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
@@ -3717,7 +3751,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Open Luximos Christie's 2026</t>
+          <t>Open Caetano</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3727,7 +3761,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3737,7 +3771,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Your Top-padel Industrial</t>
+          <t>Quinta de Monserrate Gaia</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3760,38 +3794,34 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenLuximosChristies26</t>
+          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="O43" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="O43" s="3" t="n"/>
+      <c r="P43" s="4" t="n"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R43" s="5" t="n">
-        <v>46317.50673072465</v>
+        <v>46320.39207340783</v>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>site (dado suspeito)</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
@@ -3803,7 +3833,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>III Open W Padel &amp; Ténis Parque</t>
+          <t>Gentlemen's &amp; Ladies Crew by OPA</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Oeiras</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3823,21 +3853,21 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>W Padel Ténis &amp; Parque</t>
+          <t>Oeiras Padel Academy</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>VET M&amp;F +35 a +60</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>MASTERS</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -3846,38 +3876,34 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/IIIOpenWPadelTenisParque</t>
+          <t>https://fpp.tiepadel.com/tournaments/TheGentlemenLadiesCrewOPA</t>
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>46316</v>
+        <v>46322</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="O44" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="4" t="n"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Pagamentos a decorrer</t>
+          <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R44" s="5" t="n">
-        <v>46317.50673073744</v>
+        <v>46320.39207341937</v>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>site (dado suspeito)</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -3889,7 +3915,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>II OPEN ABSOLUTOS DEZ POR VINTE by D6</t>
+          <t>Ii Open Jovem Carcavelos Ténis e Padel</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3899,7 +3925,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Carcavelos</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3909,21 +3935,21 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Dezporvinte</t>
+          <t>Carcavelos Ténis e Padel</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>M&amp;F: S12, S14, S16, S18</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -3932,7 +3958,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/IOpenABSDezporVinteByD6</t>
+          <t>/torneios/ii-open-jovem-carcavelos-tenis-e-padel-jov-2026-11-06</t>
         </is>
       </c>
       <c r="K45" s="3" t="n">
@@ -3941,41 +3967,29 @@
       <c r="L45" s="3" t="n">
         <v>46334</v>
       </c>
-      <c r="M45" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>46324</v>
-      </c>
-      <c r="P45" s="4" t="n">
-        <v>0.7083333333333334</v>
-      </c>
+      <c r="M45" s="3" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="3" t="n"/>
+      <c r="P45" s="4" t="n"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições ainda não abriram</t>
         </is>
       </c>
       <c r="R45" s="5" t="n">
-        <v>46317.50673075693</v>
+        <v>46320.39207342982</v>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+      <c r="T45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Open Caetano</t>
+          <t>Open DL Cozinhas Míele</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3985,7 +3999,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Vila Nova de Gaia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3995,7 +4009,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Quinta de Monserrate Gaia</t>
+          <t>PAC - Padel Athletic Club</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4009,7 +4023,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -4018,34 +4032,38 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/OpenCaetano26</t>
+          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>46332</v>
+        <v>46335</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="4" t="n"/>
+      <c r="O46" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>Inscrições abertas</t>
         </is>
       </c>
       <c r="R46" s="5" t="n">
-        <v>46317.50673077094</v>
+        <v>46320.3920734438</v>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>site (dado suspeito)</t>
+          <t>site</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -4057,7 +4075,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Gentlemen's &amp; Ladies Crew by OPA</t>
+          <t>I Torneio SPM</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4067,7 +4085,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Oeiras</t>
+          <t>Mafra</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4077,21 +4095,21 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Oeiras Padel Academy</t>
+          <t>Sport Padel Mafra</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>VET M&amp;F +35 a +60</t>
+          <t>F1-F6; M1-M6</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
+          <t>MAIN</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -4100,46 +4118,38 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/TheGentlemenLadiesCrewOPA</t>
+          <t>/torneios/i-torneio-spm-abs-2026-11-12</t>
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>46332</v>
+        <v>46338</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>46334</v>
-      </c>
-      <c r="M47" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="N47" s="4" t="n">
-        <v>0.625</v>
-      </c>
+        <v>46341</v>
+      </c>
+      <c r="M47" s="3" t="n"/>
+      <c r="N47" s="4" t="n"/>
       <c r="O47" s="3" t="n"/>
       <c r="P47" s="4" t="n"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições ainda não abriram</t>
         </is>
       </c>
       <c r="R47" s="5" t="n">
-        <v>46317.50673078245</v>
+        <v>46320.39207345415</v>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>site (dado suspeito)</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+          <t>site</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Ii Open Jovem Carcavelos Ténis e Padel</t>
+          <t>FINAL LIGA de CLUBES VETERANOS</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4149,7 +4159,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Carcavelos</t>
+          <t>Caldas da Rainha</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4159,22 +4169,20 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Carcavelos Ténis e Padel</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>M&amp;F: S12, S14, S16, S18</t>
+          <t>M &amp; F</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -4182,14 +4190,14 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>/torneios/ii-open-jovem-carcavelos-tenis-e-padel-jov-2026-11-06</t>
+          <t>https://fpp.tiepadel.com/tournaments/78f940e5-cf76-475a-9a6d-76aaf9daf59a</t>
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>46332</v>
+        <v>46338</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="M48" s="3" t="n"/>
       <c r="N48" s="4" t="n"/>
@@ -4201,7 +4209,7 @@
         </is>
       </c>
       <c r="R48" s="5" t="n">
-        <v>46317.50673079224</v>
+        <v>46320.39207347028</v>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
@@ -4213,7 +4221,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Open DL Cozinhas Míele</t>
+          <t>1º Open Jovem W Padel &amp; Ténis Parque</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -4223,7 +4231,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Barreiro</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -4233,21 +4241,21 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PAC - Padel Athletic Club</t>
+          <t>W Padel Ténis &amp; Parque</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>M&amp;F: S12, S14, S16, S18</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -4256,26 +4264,26 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/Tournaments/OpenDLCozinhasMiele</t>
+          <t>https://fpp.tiepadel.com/tournaments/1openJOVWPadel26</t>
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>46335</v>
+        <v>46339</v>
       </c>
       <c r="L49" s="3" t="n">
         <v>46341</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.375</v>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
@@ -4283,7 +4291,7 @@
         </is>
       </c>
       <c r="R49" s="5" t="n">
-        <v>46317.50673080547</v>
+        <v>46320.39207348135</v>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
@@ -4299,7 +4307,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>I Torneio SPM</t>
+          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4309,7 +4317,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Mafra</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4319,12 +4327,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sport Padel Mafra</t>
+          <t>FPP</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>F1-F6; M1-M6</t>
+          <t>M &amp; F</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4332,9 +4340,7 @@
           <t>MAIN</t>
         </is>
       </c>
-      <c r="H50" s="2" t="n">
-        <v>2000</v>
-      </c>
+      <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -4342,14 +4348,14 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>/torneios/i-torneio-spm-abs-2026-11-12</t>
+          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>46338</v>
+        <v>46345</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>46341</v>
+        <v>46348</v>
       </c>
       <c r="M50" s="3" t="n"/>
       <c r="N50" s="4" t="n"/>
@@ -4361,7 +4367,7 @@
         </is>
       </c>
       <c r="R50" s="5" t="n">
-        <v>46317.50673081545</v>
+        <v>46320.39207349808</v>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
@@ -4373,7 +4379,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FINAL LIGA de CLUBES VETERANOS</t>
+          <t>Masters Final FPP Jovens</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4383,7 +4389,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Caldas da Rainha</t>
+          <t>Algarve</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4396,14 +4402,10 @@
           <t>FPP</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>M &amp; F</t>
-        </is>
-      </c>
+      <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>MASTERS</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="H51" s="2" t="n"/>
@@ -4414,14 +4416,14 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/78f940e5-cf76-475a-9a6d-76aaf9daf59a</t>
+          <t>/torneios/masters-final-fpp-jovens-jov-2026-11-27</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>46338</v>
+        <v>46353</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>46341</v>
+        <v>46355</v>
       </c>
       <c r="M51" s="3" t="n"/>
       <c r="N51" s="4" t="n"/>
@@ -4433,7 +4435,7 @@
         </is>
       </c>
       <c r="R51" s="5" t="n">
-        <v>46317.50673083162</v>
+        <v>46320.39207351515</v>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
@@ -4445,7 +4447,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1º Open Jovem W Padel &amp; Ténis Parque</t>
+          <t>Masters Final FPP Veteranos</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4455,7 +4457,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Barreiro</t>
+          <t>Algarve</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4465,22 +4467,16 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>W Padel Ténis &amp; Parque</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;F: S12, S14, S16, S18</t>
-        </is>
-      </c>
+          <t>FPP</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>JUNIOR</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>5000</v>
-      </c>
+          <t>MASTERS</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Ver regulamento interno</t>
@@ -4488,50 +4484,38 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/1openJOVWPadel26</t>
+          <t>/torneios/masters-final-fpp-veteranos-vet-2026-11-27</t>
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>46339</v>
+        <v>46353</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>46341</v>
-      </c>
-      <c r="M52" s="3" t="n">
-        <v>46330</v>
-      </c>
-      <c r="N52" s="4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="O52" s="3" t="n">
-        <v>46332</v>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v>0.375</v>
-      </c>
+        <v>46355</v>
+      </c>
+      <c r="M52" s="3" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="4" t="n"/>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Inscrições abertas</t>
+          <t>Inscrições ainda não abriram</t>
         </is>
       </c>
       <c r="R52" s="5" t="n">
-        <v>46317.50673084318</v>
+        <v>46320.39207353252</v>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
           <t>site</t>
         </is>
       </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>Europe/Lisbon</t>
-        </is>
-      </c>
+      <c r="T52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FINAL LIGA de CLUBES ABSOLUTOS</t>
+          <t>Masters Final FPP Absoluto</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -4541,7 +4525,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4554,11 +4538,7 @@
           <t>FPP</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>M &amp; F</t>
-        </is>
-      </c>
+      <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>MAIN</t>
@@ -4572,14 +4552,14 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>https://fpp.tiepadel.com/tournaments/ef2c1e43-5cb2-4980-a7bb-9e7b7da110bb</t>
+          <t>/torneios/masters-final-fpp-absoluto-abs-2026-11-27</t>
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>46345</v>
+        <v>46353</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="M53" s="3" t="n"/>
       <c r="N53" s="4" t="n"/>
@@ -4591,7 +4571,7 @@
         </is>
       </c>
       <c r="R53" s="5" t="n">
-        <v>46317.50673085986</v>
+        <v>46320.39207355012</v>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
@@ -4600,212 +4580,8 @@
       </c>
       <c r="T53" s="2" t="n"/>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Masters Final FPP Jovens</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Algarve</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>JUNIOR</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>/torneios/masters-final-fpp-jovens-jov-2026-11-27</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>46353</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>46355</v>
-      </c>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="4" t="n"/>
-      <c r="O54" s="3" t="n"/>
-      <c r="P54" s="4" t="n"/>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições ainda não abriram</t>
-        </is>
-      </c>
-      <c r="R54" s="5" t="n">
-        <v>46317.50673087596</v>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Masters Final FPP Veteranos</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Algarve</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="n"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>MASTERS</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>/torneios/masters-final-fpp-veteranos-vet-2026-11-27</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>46353</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>46355</v>
-      </c>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="4" t="n"/>
-      <c r="O55" s="3" t="n"/>
-      <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições ainda não abriram</t>
-        </is>
-      </c>
-      <c r="R55" s="5" t="n">
-        <v>46317.50673089265</v>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Masters Final FPP Absoluto</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>FPP Portugal</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Paredes</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>FPP</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Ver regulamento interno</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>/torneios/masters-final-fpp-absoluto-abs-2026-11-27</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>46353</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>46355</v>
-      </c>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="4" t="n"/>
-      <c r="O56" s="3" t="n"/>
-      <c r="P56" s="4" t="n"/>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>Inscrições ainda não abriram</t>
-        </is>
-      </c>
-      <c r="R56" s="5" t="n">
-        <v>46317.50673090955</v>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>site</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T56"/>
+  <autoFilter ref="A1:T53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>